--- a/templates/construction-protection-overtime-sample.xlsx
+++ b/templates/construction-protection-overtime-sample.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="14835"/>
+    <workbookView windowHeight="16305"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="116">
   <si>
     <t>图例</t>
   </si>
@@ -225,10 +225,13 @@
     <t>补工队</t>
   </si>
   <si>
+    <t>每月周末需要手动标黄</t>
+  </si>
+  <si>
     <t>12日</t>
   </si>
   <si>
-    <t>每月周末需要手动标黄</t>
+    <t>11-17日为填表示范</t>
   </si>
   <si>
     <t>13日</t>
@@ -264,7 +267,10 @@
     <t>岩质坡面排查驻</t>
   </si>
   <si>
-    <t>11-17日为填表示范</t>
+    <t>工区文字版日计划样本</t>
+  </si>
+  <si>
+    <t>工区文字版施工点计划样本</t>
   </si>
   <si>
     <t>14日</t>
@@ -286,6 +292,51 @@
   </si>
   <si>
     <t>课件制作比赛</t>
+  </si>
+  <si>
+    <t>XX工区2026年7月31日计划
+上午
+作业里程：
+作业时间：
+作业项目：
+作业负责人：
+驻站富文：
+工地防护：
+中间防护：
+作业人员：
+作业工具：
+下午
+作业里程：
+作业时间：
+作业项目：
+作业负责人：
+驻站富文：
+工地防护：
+中间防护：
+作业人员：
+作业工具：
+室内：
+（其他非上道作业）
+防洪三项：负责：  驻站：  工地：
+（其他施工点）
+补休：
+探亲：
+事假： 
+（其他假期）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026年7月31日富文防洪三项
+作业里程:
+作业项目：
+作业时间：5:00—10:30
+15:00-18:30
+作业负责人:
+驻站富文：
+工地防护员：
+作业人员：民工15人，职工3人。
+作业机具：
+跨线里程：
+</t>
   </si>
   <si>
     <t>15日</t>
@@ -1540,7 +1591,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1615,15 +1666,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1636,9 +1681,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1675,6 +1717,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1686,9 +1731,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1732,24 +1774,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2089,7 +2113,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BB69"/>
+  <dimension ref="A1:BC69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.88333333333333" style="1" customWidth="1"/>
@@ -2098,7 +2122,8 @@
     <col min="18" max="52" width="5.66666666666667" style="1" customWidth="1"/>
     <col min="53" max="53" width="9" style="1" customWidth="1"/>
     <col min="54" max="54" width="38.6666666666667" style="1" customWidth="1"/>
-    <col min="55" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="55" max="55" width="41.025" style="1" customWidth="1"/>
+    <col min="56" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:54">
@@ -2486,43 +2511,43 @@
       <c r="E5" s="25"/>
       <c r="F5" s="26"/>
       <c r="G5" s="27"/>
-      <c r="H5" s="28"/>
+      <c r="H5" s="25"/>
       <c r="I5" s="26"/>
       <c r="J5" s="27"/>
       <c r="K5" s="25"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
-      <c r="N5" s="28"/>
+      <c r="N5" s="25"/>
       <c r="O5" s="26"/>
       <c r="P5" s="27"/>
-      <c r="Q5" s="28"/>
+      <c r="Q5" s="25"/>
       <c r="R5" s="26"/>
       <c r="S5" s="27"/>
       <c r="T5" s="25"/>
       <c r="U5" s="26"/>
       <c r="V5" s="27"/>
-      <c r="W5" s="28"/>
+      <c r="W5" s="25"/>
       <c r="X5" s="26"/>
       <c r="Y5" s="27"/>
-      <c r="Z5" s="28"/>
+      <c r="Z5" s="25"/>
       <c r="AA5" s="26"/>
       <c r="AB5" s="27"/>
-      <c r="AC5" s="29"/>
+      <c r="AC5" s="28"/>
       <c r="AD5" s="26"/>
       <c r="AE5" s="27"/>
-      <c r="AF5" s="28"/>
+      <c r="AF5" s="25"/>
       <c r="AG5" s="26"/>
       <c r="AH5" s="27"/>
-      <c r="AI5" s="28"/>
+      <c r="AI5" s="25"/>
       <c r="AJ5" s="26"/>
       <c r="AK5" s="27"/>
       <c r="AL5" s="25"/>
       <c r="AM5" s="26"/>
       <c r="AN5" s="27"/>
-      <c r="AO5" s="28"/>
+      <c r="AO5" s="25"/>
       <c r="AP5" s="26"/>
       <c r="AQ5" s="27"/>
-      <c r="AR5" s="28"/>
+      <c r="AR5" s="25"/>
       <c r="AS5" s="26"/>
       <c r="AT5" s="27"/>
       <c r="AU5" s="25"/>
@@ -2536,3033 +2561,3085 @@
       </c>
     </row>
     <row r="6" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="24" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="25"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="32"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="25"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="32"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="30"/>
       <c r="K6" s="25"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="32"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="30"/>
       <c r="T6" s="25"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="32"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="31"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="31"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="31"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="31"/>
-      <c r="AH6" s="32"/>
-      <c r="AI6" s="28"/>
-      <c r="AJ6" s="31"/>
-      <c r="AK6" s="32"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="25"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="25"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="30"/>
       <c r="AL6" s="25"/>
-      <c r="AM6" s="31"/>
-      <c r="AN6" s="32"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="30"/>
       <c r="AO6" s="25"/>
-      <c r="AP6" s="31"/>
-      <c r="AQ6" s="32"/>
-      <c r="AR6" s="28"/>
-      <c r="AS6" s="31"/>
-      <c r="AT6" s="32"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="30"/>
+      <c r="AR6" s="25"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="30"/>
       <c r="AU6" s="25"/>
-      <c r="AV6" s="31"/>
-      <c r="AW6" s="32"/>
+      <c r="AV6" s="29"/>
+      <c r="AW6" s="30"/>
       <c r="AX6" s="25"/>
-      <c r="AY6" s="31"/>
-      <c r="AZ6" s="32"/>
+      <c r="AY6" s="29"/>
+      <c r="AZ6" s="30"/>
       <c r="BA6" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="32"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="25"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="32"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="30"/>
       <c r="K7" s="25"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="32"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="30"/>
       <c r="T7" s="25"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="32"/>
-      <c r="W7" s="28"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="32"/>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="31"/>
-      <c r="AB7" s="32"/>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="31"/>
-      <c r="AE7" s="32"/>
-      <c r="AF7" s="28"/>
-      <c r="AG7" s="31"/>
-      <c r="AH7" s="32"/>
-      <c r="AI7" s="28"/>
-      <c r="AJ7" s="31"/>
-      <c r="AK7" s="32"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="25"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="30"/>
       <c r="AL7" s="25"/>
-      <c r="AM7" s="31"/>
-      <c r="AN7" s="32"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="30"/>
       <c r="AO7" s="25"/>
-      <c r="AP7" s="31"/>
-      <c r="AQ7" s="32"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="30"/>
       <c r="AR7" s="25"/>
-      <c r="AS7" s="31"/>
-      <c r="AT7" s="32"/>
-      <c r="AU7" s="28"/>
-      <c r="AV7" s="31"/>
-      <c r="AW7" s="32"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="30"/>
+      <c r="AU7" s="25"/>
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="30"/>
       <c r="AX7" s="25"/>
-      <c r="AY7" s="31"/>
-      <c r="AZ7" s="32"/>
+      <c r="AY7" s="29"/>
+      <c r="AZ7" s="30"/>
       <c r="BA7" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="32"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="32"/>
-      <c r="W8" s="35"/>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="32"/>
-      <c r="Z8" s="34"/>
-      <c r="AA8" s="31"/>
-      <c r="AB8" s="32"/>
-      <c r="AC8" s="34"/>
-      <c r="AD8" s="31"/>
-      <c r="AE8" s="32"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="31"/>
-      <c r="AH8" s="32"/>
-      <c r="AI8" s="34"/>
-      <c r="AJ8" s="31"/>
-      <c r="AK8" s="32"/>
-      <c r="AL8" s="34"/>
-      <c r="AM8" s="31"/>
-      <c r="AN8" s="32"/>
-      <c r="AO8" s="34"/>
-      <c r="AP8" s="31"/>
-      <c r="AQ8" s="32"/>
-      <c r="AR8" s="34"/>
-      <c r="AS8" s="31"/>
-      <c r="AT8" s="32"/>
-      <c r="AU8" s="36"/>
-      <c r="AV8" s="31"/>
-      <c r="AW8" s="32"/>
-      <c r="AX8" s="34"/>
-      <c r="AY8" s="31"/>
-      <c r="AZ8" s="32"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="32"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="32"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="32"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="32"/>
+      <c r="AG8" s="29"/>
+      <c r="AH8" s="30"/>
+      <c r="AI8" s="32"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="32"/>
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="30"/>
+      <c r="AO8" s="32"/>
+      <c r="AP8" s="29"/>
+      <c r="AQ8" s="30"/>
+      <c r="AR8" s="32"/>
+      <c r="AS8" s="29"/>
+      <c r="AT8" s="30"/>
+      <c r="AU8" s="33"/>
+      <c r="AV8" s="29"/>
+      <c r="AW8" s="30"/>
+      <c r="AX8" s="32"/>
+      <c r="AY8" s="29"/>
+      <c r="AZ8" s="30"/>
       <c r="BA8" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="32"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="32"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="34"/>
-      <c r="AA9" s="31"/>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="34"/>
-      <c r="AD9" s="31"/>
-      <c r="AE9" s="32"/>
-      <c r="AF9" s="34"/>
-      <c r="AG9" s="31"/>
-      <c r="AH9" s="32"/>
-      <c r="AI9" s="34"/>
-      <c r="AJ9" s="31"/>
-      <c r="AK9" s="32"/>
-      <c r="AL9" s="34"/>
-      <c r="AM9" s="31"/>
-      <c r="AN9" s="32"/>
-      <c r="AO9" s="34"/>
-      <c r="AP9" s="31"/>
-      <c r="AQ9" s="32"/>
-      <c r="AR9" s="34"/>
-      <c r="AS9" s="31"/>
-      <c r="AT9" s="32"/>
-      <c r="AU9" s="36"/>
-      <c r="AV9" s="31"/>
-      <c r="AW9" s="32"/>
-      <c r="AX9" s="34"/>
-      <c r="AY9" s="31"/>
-      <c r="AZ9" s="32"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="32"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="32"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="32"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="32"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="32"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="32"/>
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="32"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="32"/>
+      <c r="AP9" s="29"/>
+      <c r="AQ9" s="30"/>
+      <c r="AR9" s="32"/>
+      <c r="AS9" s="29"/>
+      <c r="AT9" s="30"/>
+      <c r="AU9" s="33"/>
+      <c r="AV9" s="29"/>
+      <c r="AW9" s="30"/>
+      <c r="AX9" s="32"/>
+      <c r="AY9" s="29"/>
+      <c r="AZ9" s="30"/>
       <c r="BA9" s="9" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30"/>
       <c r="E10" s="25"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="32"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="30"/>
       <c r="K10" s="25"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="28"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="32"/>
-      <c r="T10" s="28"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="32"/>
-      <c r="W10" s="28"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="28"/>
-      <c r="AA10" s="31"/>
-      <c r="AB10" s="32"/>
-      <c r="AC10" s="28"/>
-      <c r="AD10" s="31"/>
-      <c r="AE10" s="32"/>
-      <c r="AF10" s="28"/>
-      <c r="AG10" s="31"/>
-      <c r="AH10" s="32"/>
-      <c r="AI10" s="28"/>
-      <c r="AJ10" s="31"/>
-      <c r="AK10" s="32"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="29"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="25"/>
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="30"/>
       <c r="AL10" s="25"/>
-      <c r="AM10" s="31"/>
-      <c r="AN10" s="32"/>
-      <c r="AO10" s="28"/>
-      <c r="AP10" s="31"/>
-      <c r="AQ10" s="32"/>
-      <c r="AR10" s="28"/>
-      <c r="AS10" s="31"/>
-      <c r="AT10" s="32"/>
-      <c r="AU10" s="28"/>
-      <c r="AV10" s="31"/>
-      <c r="AW10" s="32"/>
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="30"/>
+      <c r="AO10" s="25"/>
+      <c r="AP10" s="29"/>
+      <c r="AQ10" s="30"/>
+      <c r="AR10" s="25"/>
+      <c r="AS10" s="29"/>
+      <c r="AT10" s="30"/>
+      <c r="AU10" s="25"/>
+      <c r="AV10" s="29"/>
+      <c r="AW10" s="30"/>
       <c r="AX10" s="25"/>
-      <c r="AY10" s="31"/>
-      <c r="AZ10" s="32"/>
+      <c r="AY10" s="29"/>
+      <c r="AZ10" s="30"/>
       <c r="BA10" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="32"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="25"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="32"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="30"/>
       <c r="K11" s="25"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="28"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="32"/>
-      <c r="T11" s="28"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="32"/>
-      <c r="W11" s="28"/>
-      <c r="X11" s="31"/>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="28"/>
-      <c r="AA11" s="31"/>
-      <c r="AB11" s="32"/>
-      <c r="AC11" s="28"/>
-      <c r="AD11" s="31"/>
-      <c r="AE11" s="32"/>
-      <c r="AF11" s="28"/>
-      <c r="AG11" s="31"/>
-      <c r="AH11" s="32"/>
-      <c r="AI11" s="28"/>
-      <c r="AJ11" s="31"/>
-      <c r="AK11" s="32"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="29"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="25"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="30"/>
       <c r="AL11" s="25"/>
-      <c r="AM11" s="31"/>
-      <c r="AN11" s="32"/>
-      <c r="AO11" s="28"/>
-      <c r="AP11" s="31"/>
-      <c r="AQ11" s="32"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="30"/>
+      <c r="AO11" s="25"/>
+      <c r="AP11" s="29"/>
+      <c r="AQ11" s="30"/>
       <c r="AR11" s="25"/>
-      <c r="AS11" s="31"/>
-      <c r="AT11" s="32"/>
-      <c r="AU11" s="28"/>
-      <c r="AV11" s="31"/>
-      <c r="AW11" s="32"/>
-      <c r="AX11" s="28"/>
-      <c r="AY11" s="31"/>
-      <c r="AZ11" s="32"/>
+      <c r="AS11" s="29"/>
+      <c r="AT11" s="30"/>
+      <c r="AU11" s="25"/>
+      <c r="AV11" s="29"/>
+      <c r="AW11" s="30"/>
+      <c r="AX11" s="25"/>
+      <c r="AY11" s="29"/>
+      <c r="AZ11" s="30"/>
       <c r="BA11" s="9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="32"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="30"/>
       <c r="K12" s="25"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="28"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="32"/>
-      <c r="T12" s="28"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="32"/>
-      <c r="W12" s="28"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="32"/>
-      <c r="Z12" s="28"/>
-      <c r="AA12" s="31"/>
-      <c r="AB12" s="32"/>
-      <c r="AC12" s="28"/>
-      <c r="AD12" s="31"/>
-      <c r="AE12" s="32"/>
-      <c r="AF12" s="28"/>
-      <c r="AG12" s="31"/>
-      <c r="AH12" s="32"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="29"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="29"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="29"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="29"/>
+      <c r="AH12" s="30"/>
       <c r="AI12" s="25"/>
-      <c r="AJ12" s="31"/>
-      <c r="AK12" s="32"/>
-      <c r="AL12" s="28"/>
-      <c r="AM12" s="31"/>
-      <c r="AN12" s="32"/>
-      <c r="AO12" s="28"/>
-      <c r="AP12" s="31"/>
-      <c r="AQ12" s="32"/>
-      <c r="AR12" s="28"/>
-      <c r="AS12" s="31"/>
-      <c r="AT12" s="32"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="25"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="30"/>
+      <c r="AO12" s="25"/>
+      <c r="AP12" s="29"/>
+      <c r="AQ12" s="30"/>
+      <c r="AR12" s="25"/>
+      <c r="AS12" s="29"/>
+      <c r="AT12" s="30"/>
       <c r="AU12" s="25"/>
-      <c r="AV12" s="31"/>
-      <c r="AW12" s="32"/>
+      <c r="AV12" s="29"/>
+      <c r="AW12" s="30"/>
       <c r="AX12" s="25"/>
-      <c r="AY12" s="31"/>
-      <c r="AZ12" s="32"/>
-      <c r="BA12" s="38" t="s">
+      <c r="AY12" s="29"/>
+      <c r="AZ12" s="30"/>
+      <c r="BA12" s="35" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="32"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="25"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="28"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="28"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="28"/>
-      <c r="AA13" s="31"/>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="31"/>
-      <c r="AE13" s="32"/>
-      <c r="AF13" s="28"/>
-      <c r="AG13" s="31"/>
-      <c r="AH13" s="32"/>
-      <c r="AI13" s="28"/>
-      <c r="AJ13" s="31"/>
-      <c r="AK13" s="32"/>
-      <c r="AL13" s="28"/>
-      <c r="AM13" s="31"/>
-      <c r="AN13" s="32"/>
-      <c r="AO13" s="28"/>
-      <c r="AP13" s="31"/>
-      <c r="AQ13" s="32"/>
-      <c r="AR13" s="28"/>
-      <c r="AS13" s="31"/>
-      <c r="AT13" s="32"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="30"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="30"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="29"/>
+      <c r="AH13" s="30"/>
+      <c r="AI13" s="25"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="30"/>
+      <c r="AL13" s="25"/>
+      <c r="AM13" s="29"/>
+      <c r="AN13" s="30"/>
+      <c r="AO13" s="25"/>
+      <c r="AP13" s="29"/>
+      <c r="AQ13" s="30"/>
+      <c r="AR13" s="25"/>
+      <c r="AS13" s="29"/>
+      <c r="AT13" s="30"/>
       <c r="AU13" s="25"/>
-      <c r="AV13" s="31"/>
-      <c r="AW13" s="32"/>
+      <c r="AV13" s="29"/>
+      <c r="AW13" s="30"/>
       <c r="AX13" s="25"/>
-      <c r="AY13" s="31"/>
-      <c r="AZ13" s="32"/>
-      <c r="BA13" s="38" t="s">
+      <c r="AY13" s="29"/>
+      <c r="AZ13" s="30"/>
+      <c r="BA13" s="35" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="30"/>
       <c r="H14" s="25"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="28"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="32"/>
-      <c r="T14" s="28"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="32"/>
-      <c r="W14" s="28"/>
-      <c r="X14" s="31"/>
-      <c r="Y14" s="32"/>
-      <c r="Z14" s="28"/>
-      <c r="AA14" s="31"/>
-      <c r="AB14" s="32"/>
-      <c r="AC14" s="28"/>
-      <c r="AD14" s="31"/>
-      <c r="AE14" s="32"/>
-      <c r="AF14" s="28"/>
-      <c r="AG14" s="31"/>
-      <c r="AH14" s="32"/>
-      <c r="AI14" s="28"/>
-      <c r="AJ14" s="31"/>
-      <c r="AK14" s="32"/>
-      <c r="AL14" s="28"/>
-      <c r="AM14" s="31"/>
-      <c r="AN14" s="32"/>
-      <c r="AO14" s="28"/>
-      <c r="AP14" s="31"/>
-      <c r="AQ14" s="32"/>
-      <c r="AR14" s="28"/>
-      <c r="AS14" s="31"/>
-      <c r="AT14" s="32"/>
-      <c r="AU14" s="28"/>
-      <c r="AV14" s="31"/>
-      <c r="AW14" s="32"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="30"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="30"/>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="25"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="25"/>
+      <c r="AM14" s="29"/>
+      <c r="AN14" s="30"/>
+      <c r="AO14" s="25"/>
+      <c r="AP14" s="29"/>
+      <c r="AQ14" s="30"/>
+      <c r="AR14" s="25"/>
+      <c r="AS14" s="29"/>
+      <c r="AT14" s="30"/>
+      <c r="AU14" s="25"/>
+      <c r="AV14" s="29"/>
+      <c r="AW14" s="30"/>
       <c r="AX14" s="25"/>
-      <c r="AY14" s="31"/>
-      <c r="AZ14" s="32"/>
+      <c r="AY14" s="29"/>
+      <c r="AZ14" s="30"/>
       <c r="BA14" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="36" t="s">
         <v>50</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="38"/>
       <c r="E15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="38"/>
       <c r="H15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I15" s="40"/>
-      <c r="J15" s="41"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="38"/>
       <c r="K15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="L15" s="40"/>
-      <c r="M15" s="41"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="38"/>
       <c r="N15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="O15" s="40"/>
-      <c r="P15" s="41"/>
+      <c r="O15" s="37"/>
+      <c r="P15" s="38"/>
       <c r="Q15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R15" s="40"/>
-      <c r="S15" s="41"/>
+      <c r="R15" s="37"/>
+      <c r="S15" s="38"/>
       <c r="T15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="U15" s="40"/>
-      <c r="V15" s="41"/>
+      <c r="U15" s="37"/>
+      <c r="V15" s="38"/>
       <c r="W15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="X15" s="40"/>
-      <c r="Y15" s="41"/>
+      <c r="X15" s="37"/>
+      <c r="Y15" s="38"/>
       <c r="Z15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AA15" s="40"/>
-      <c r="AB15" s="41"/>
+      <c r="AA15" s="37"/>
+      <c r="AB15" s="38"/>
       <c r="AC15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AD15" s="40"/>
-      <c r="AE15" s="41"/>
+      <c r="AD15" s="37"/>
+      <c r="AE15" s="38"/>
       <c r="AF15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AG15" s="40"/>
-      <c r="AH15" s="41"/>
+      <c r="AG15" s="37"/>
+      <c r="AH15" s="38"/>
       <c r="AI15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AJ15" s="40"/>
-      <c r="AK15" s="41"/>
+      <c r="AJ15" s="37"/>
+      <c r="AK15" s="38"/>
       <c r="AL15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AM15" s="40"/>
-      <c r="AN15" s="41"/>
+      <c r="AM15" s="37"/>
+      <c r="AN15" s="38"/>
       <c r="AO15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AP15" s="40"/>
-      <c r="AQ15" s="41"/>
-      <c r="AR15" s="42" t="s">
+      <c r="AP15" s="37"/>
+      <c r="AQ15" s="38"/>
+      <c r="AR15" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="AS15" s="40"/>
-      <c r="AT15" s="41"/>
-      <c r="AU15" s="42" t="s">
+      <c r="AS15" s="37"/>
+      <c r="AT15" s="38"/>
+      <c r="AU15" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="AV15" s="40"/>
-      <c r="AW15" s="41"/>
-      <c r="AX15" s="43"/>
-      <c r="AY15" s="40"/>
-      <c r="AZ15" s="41"/>
+      <c r="AV15" s="37"/>
+      <c r="AW15" s="38"/>
+      <c r="AX15" s="40"/>
+      <c r="AY15" s="37"/>
+      <c r="AZ15" s="38"/>
       <c r="BA15" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="BB15" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A16" s="39" t="s">
-        <v>52</v>
+      <c r="A16" s="36" t="s">
+        <v>53</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="41"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="38"/>
       <c r="E16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="38"/>
       <c r="H16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I16" s="40"/>
-      <c r="J16" s="41"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="38"/>
       <c r="K16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="L16" s="40"/>
-      <c r="M16" s="41"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="38"/>
       <c r="N16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="O16" s="40"/>
-      <c r="P16" s="41"/>
+      <c r="O16" s="37"/>
+      <c r="P16" s="38"/>
       <c r="Q16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R16" s="40"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="40"/>
-      <c r="V16" s="41"/>
+      <c r="R16" s="37"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="40"/>
+      <c r="U16" s="37"/>
+      <c r="V16" s="38"/>
       <c r="W16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="X16" s="40"/>
-      <c r="Y16" s="41"/>
+      <c r="X16" s="37"/>
+      <c r="Y16" s="38"/>
       <c r="Z16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AA16" s="40"/>
-      <c r="AB16" s="41"/>
-      <c r="AC16" s="43"/>
-      <c r="AD16" s="40"/>
-      <c r="AE16" s="41"/>
+      <c r="AA16" s="37"/>
+      <c r="AB16" s="38"/>
+      <c r="AC16" s="40"/>
+      <c r="AD16" s="37"/>
+      <c r="AE16" s="38"/>
       <c r="AF16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AG16" s="40"/>
-      <c r="AH16" s="41"/>
-      <c r="AI16" s="43"/>
-      <c r="AJ16" s="40"/>
-      <c r="AK16" s="41"/>
-      <c r="AL16" s="43"/>
-      <c r="AM16" s="40"/>
-      <c r="AN16" s="41"/>
+      <c r="AG16" s="37"/>
+      <c r="AH16" s="38"/>
+      <c r="AI16" s="40"/>
+      <c r="AJ16" s="37"/>
+      <c r="AK16" s="38"/>
+      <c r="AL16" s="40"/>
+      <c r="AM16" s="37"/>
+      <c r="AN16" s="38"/>
       <c r="AO16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AP16" s="40"/>
-      <c r="AQ16" s="41"/>
-      <c r="AR16" s="42" t="s">
+      <c r="AP16" s="37"/>
+      <c r="AQ16" s="38"/>
+      <c r="AR16" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="AS16" s="40"/>
-      <c r="AT16" s="41"/>
-      <c r="AU16" s="42" t="s">
+      <c r="AS16" s="37"/>
+      <c r="AT16" s="38"/>
+      <c r="AU16" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="AV16" s="40"/>
-      <c r="AW16" s="41"/>
-      <c r="AX16" s="43"/>
-      <c r="AY16" s="40"/>
-      <c r="AZ16" s="41"/>
-      <c r="BA16" s="1"/>
+      <c r="AV16" s="37"/>
+      <c r="AW16" s="38"/>
+      <c r="AX16" s="40"/>
+      <c r="AY16" s="37"/>
+      <c r="AZ16" s="38"/>
       <c r="BB16" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A17" s="37" t="s">
         <v>54</v>
       </c>
+    </row>
+    <row r="17" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A17" s="34" t="s">
+        <v>55</v>
+      </c>
       <c r="B17" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="45" t="s">
+      <c r="C17" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="44" t="s">
+      <c r="D17" s="38"/>
+      <c r="E17" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17" s="38"/>
+      <c r="H17" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="I17" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="38"/>
+      <c r="K17" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" s="41"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="O17" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="R17" s="41"/>
+      <c r="S17" s="38"/>
+      <c r="T17" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="U17" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="V17" s="38"/>
+      <c r="W17" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="X17" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y17" s="38"/>
+      <c r="Z17" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA17" s="41"/>
+      <c r="AB17" s="38"/>
+      <c r="AC17" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD17" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE17" s="38"/>
+      <c r="AF17" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG17" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH17" s="38"/>
+      <c r="AI17" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ17" s="41"/>
+      <c r="AK17" s="38"/>
+      <c r="AL17" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM17" s="41"/>
+      <c r="AN17" s="38"/>
+      <c r="AO17" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP17" s="41"/>
+      <c r="AQ17" s="38"/>
+      <c r="AR17" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS17" s="41"/>
+      <c r="AT17" s="38"/>
+      <c r="AU17" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="AV17" s="41"/>
+      <c r="AW17" s="38"/>
+      <c r="AX17" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AY17" s="41"/>
+      <c r="AZ17" s="38"/>
+      <c r="BB17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BC17" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A18" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G17" s="41"/>
-      <c r="H17" s="46" t="s">
+      <c r="C18" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="38"/>
+      <c r="E18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="38"/>
+      <c r="H18" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="I18" s="37"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="L18" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="M18" s="38"/>
+      <c r="N18" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="O18" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="R18" s="37"/>
+      <c r="S18" s="38"/>
+      <c r="T18" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="I17" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="J17" s="41"/>
-      <c r="K17" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="L17" s="44"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="O17" s="44" t="s">
+      <c r="U18" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="V18" s="38"/>
+      <c r="W18" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="X18" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y18" s="38"/>
+      <c r="Z18" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA18" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB18" s="38"/>
+      <c r="AC18" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD18" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE18" s="38"/>
+      <c r="AF18" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG18" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH18" s="38"/>
+      <c r="AI18" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ18" s="37"/>
+      <c r="AK18" s="38"/>
+      <c r="AL18" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM18" s="37"/>
+      <c r="AN18" s="38"/>
+      <c r="AO18" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP18" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="AQ18" s="38"/>
+      <c r="AR18" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS18" s="37"/>
+      <c r="AT18" s="38"/>
+      <c r="AU18" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="AV18" s="37"/>
+      <c r="AW18" s="38"/>
+      <c r="AX18" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY18" s="37"/>
+      <c r="AZ18" s="38"/>
+      <c r="BB18" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC18" s="45" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A19" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="R17" s="44"/>
-      <c r="S17" s="41"/>
-      <c r="T17" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="U17" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="V17" s="41"/>
-      <c r="W17" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="X17" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y17" s="41"/>
-      <c r="Z17" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA17" s="44"/>
-      <c r="AB17" s="41"/>
-      <c r="AC17" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD17" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE17" s="41"/>
-      <c r="AF17" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG17" s="44" t="s">
+      <c r="C19" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="38"/>
+      <c r="E19" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="37"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="AH17" s="41"/>
-      <c r="AI17" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ17" s="44"/>
-      <c r="AK17" s="41"/>
-      <c r="AL17" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="AM17" s="44"/>
-      <c r="AN17" s="41"/>
-      <c r="AO17" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP17" s="44"/>
-      <c r="AQ17" s="41"/>
-      <c r="AR17" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="AS17" s="44"/>
-      <c r="AT17" s="41"/>
-      <c r="AU17" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="AV17" s="44"/>
-      <c r="AW17" s="41"/>
-      <c r="AX17" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="AY17" s="44"/>
-      <c r="AZ17" s="41"/>
-      <c r="BA17" s="1"/>
-      <c r="BB17" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A18" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="41"/>
-      <c r="H18" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="40"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="L18" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="M18" s="41"/>
-      <c r="N18" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="O18" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="R18" s="40"/>
-      <c r="S18" s="41"/>
-      <c r="T18" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="U18" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="V18" s="41"/>
-      <c r="W18" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="X18" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y18" s="41"/>
-      <c r="Z18" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA18" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB18" s="41"/>
-      <c r="AC18" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD18" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE18" s="41"/>
-      <c r="AF18" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG18" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="AH18" s="41"/>
-      <c r="AI18" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ18" s="40"/>
-      <c r="AK18" s="41"/>
-      <c r="AL18" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="AM18" s="40"/>
-      <c r="AN18" s="41"/>
-      <c r="AO18" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="AP18" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="AQ18" s="41"/>
-      <c r="AR18" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="AS18" s="40"/>
-      <c r="AT18" s="41"/>
-      <c r="AU18" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="AV18" s="40"/>
-      <c r="AW18" s="41"/>
-      <c r="AX18" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="AY18" s="40"/>
-      <c r="AZ18" s="41"/>
-    </row>
-    <row r="19" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A19" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="43" t="s">
-        <v>75</v>
-      </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="I19" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="J19" s="41"/>
+      <c r="I19" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" s="38"/>
       <c r="K19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L19" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="M19" s="41"/>
+      <c r="L19" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="M19" s="38"/>
       <c r="N19" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="O19" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="R19" s="40"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="42" t="s">
+      <c r="O19" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="R19" s="37"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="U19" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="V19" s="41"/>
+      <c r="U19" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="V19" s="38"/>
       <c r="W19" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="X19" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y19" s="38"/>
+      <c r="Z19" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="X19" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y19" s="41"/>
-      <c r="Z19" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA19" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB19" s="41"/>
+      <c r="AA19" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB19" s="38"/>
       <c r="AC19" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD19" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE19" s="41"/>
+        <v>60</v>
+      </c>
+      <c r="AD19" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE19" s="38"/>
       <c r="AF19" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG19" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH19" s="41"/>
-      <c r="AI19" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="AJ19" s="40"/>
-      <c r="AK19" s="41"/>
-      <c r="AL19" s="43" t="s">
+      <c r="AG19" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH19" s="38"/>
+      <c r="AI19" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ19" s="37"/>
+      <c r="AK19" s="38"/>
+      <c r="AL19" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM19" s="37"/>
+      <c r="AN19" s="38"/>
+      <c r="AO19" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP19" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="AQ19" s="38"/>
+      <c r="AR19" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="AM19" s="40"/>
-      <c r="AN19" s="41"/>
-      <c r="AO19" s="5" t="s">
+      <c r="AS19" s="37"/>
+      <c r="AT19" s="38"/>
+      <c r="AU19" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="AV19" s="37"/>
+      <c r="AW19" s="38"/>
+      <c r="AX19" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="AY19" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ19" s="38"/>
+      <c r="BB19" s="45"/>
+      <c r="BC19" s="45"/>
+    </row>
+    <row r="20" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A20" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="37"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="38">
+        <v>1</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20" s="38"/>
+      <c r="K20" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="L20" s="37"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="O20" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="R20" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="S20" s="38">
+        <v>1</v>
+      </c>
+      <c r="T20" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="U20" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="V20" s="38"/>
+      <c r="W20" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="X20" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y20" s="38">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA20" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB20" s="38">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD20" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE20" s="38"/>
+      <c r="AF20" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG20" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="AH20" s="38">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="AP19" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="AQ19" s="41"/>
-      <c r="AR19" s="43" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS19" s="40"/>
-      <c r="AT19" s="41"/>
-      <c r="AU19" s="42" t="s">
+      <c r="AJ20" s="37"/>
+      <c r="AK20" s="38"/>
+      <c r="AL20" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM20" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="AN20" s="38"/>
+      <c r="AO20" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP20" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="AQ20" s="38">
+        <v>1</v>
+      </c>
+      <c r="AR20" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="AV19" s="40"/>
-      <c r="AW19" s="41"/>
-      <c r="AX19" s="42" t="s">
+      <c r="AS20" s="37"/>
+      <c r="AT20" s="38"/>
+      <c r="AU20" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="AV20" s="37"/>
+      <c r="AW20" s="38"/>
+      <c r="AX20" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="AY19" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="AZ19" s="41"/>
-    </row>
-    <row r="20" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A20" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="G20" s="41">
+      <c r="AY20" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="AZ20" s="38"/>
+      <c r="BB20" s="45"/>
+      <c r="BC20" s="45"/>
+    </row>
+    <row r="21" ht="21" customHeight="1" spans="1:55">
+      <c r="A21" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="38">
         <v>1</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I20" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="J20" s="41"/>
-      <c r="K20" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="L20" s="40"/>
-      <c r="M20" s="41"/>
-      <c r="N20" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="O20" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="R20" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="S20" s="41">
+      <c r="H21" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="J21" s="38"/>
+      <c r="K21" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="L21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="M21" s="38"/>
+      <c r="N21" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="O21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="R21" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="S21" s="38">
         <v>1</v>
       </c>
-      <c r="T20" s="46" t="s">
+      <c r="T21" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="U20" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="V20" s="41"/>
-      <c r="W20" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="X20" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y20" s="41">
+      <c r="U21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="V21" s="38"/>
+      <c r="W21" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="X21" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y21" s="38">
         <v>1</v>
       </c>
-      <c r="Z20" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA20" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB20" s="41">
+      <c r="Z21" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA21" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB21" s="38">
         <v>1</v>
       </c>
-      <c r="AC20" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD20" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="AE20" s="41"/>
-      <c r="AF20" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG20" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH20" s="41">
+      <c r="AC21" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE21" s="38"/>
+      <c r="AF21" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG21" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH21" s="38">
         <v>1</v>
       </c>
-      <c r="AI20" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ20" s="40"/>
-      <c r="AK20" s="41"/>
-      <c r="AL20" s="46" t="s">
+      <c r="AI21" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ21" s="37"/>
+      <c r="AK21" s="38"/>
+      <c r="AL21" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="AM21" s="37"/>
+      <c r="AN21" s="38"/>
+      <c r="AO21" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP21" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="AQ21" s="38">
+        <v>1</v>
+      </c>
+      <c r="AR21" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="AM20" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="AN20" s="41"/>
-      <c r="AO20" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="AP20" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="AQ20" s="41">
-        <v>1</v>
-      </c>
-      <c r="AR20" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="AS20" s="40"/>
-      <c r="AT20" s="41"/>
-      <c r="AU20" s="46" t="s">
-        <v>40</v>
-      </c>
-      <c r="AV20" s="40"/>
-      <c r="AW20" s="41"/>
-      <c r="AX20" s="46" t="s">
+      <c r="AS21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT21" s="38"/>
+      <c r="AU21" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="AY20" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="AZ20" s="41"/>
-    </row>
-    <row r="21" ht="21" customHeight="1" spans="1:54">
-      <c r="A21" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="41">
-        <v>1</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I21" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="J21" s="41"/>
-      <c r="K21" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="L21" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="M21" s="41"/>
-      <c r="N21" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="O21" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="R21" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="S21" s="41">
-        <v>1</v>
-      </c>
-      <c r="T21" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="U21" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="V21" s="41"/>
-      <c r="W21" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="X21" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y21" s="41">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="45" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA21" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB21" s="41">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD21" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="AE21" s="41"/>
-      <c r="AF21" s="45" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG21" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="AH21" s="41">
-        <v>1</v>
-      </c>
-      <c r="AI21" s="47" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ21" s="40"/>
-      <c r="AK21" s="41"/>
-      <c r="AL21" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="AM21" s="40"/>
-      <c r="AN21" s="41"/>
-      <c r="AO21" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="AP21" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="AQ21" s="41">
-        <v>1</v>
-      </c>
-      <c r="AR21" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="AS21" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="AT21" s="41"/>
-      <c r="AU21" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="AV21" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="AW21" s="41"/>
-      <c r="AX21" s="47" t="s">
-        <v>69</v>
-      </c>
-      <c r="AY21" s="40"/>
-      <c r="AZ21" s="41"/>
-    </row>
-    <row r="22" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A22" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
+      <c r="AV21" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW21" s="38"/>
+      <c r="AX21" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="AY21" s="37"/>
+      <c r="AZ21" s="38"/>
+      <c r="BB21" s="45"/>
+      <c r="BC21" s="45"/>
+    </row>
+    <row r="22" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A22" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="30"/>
       <c r="E22" s="25"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="32"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="30"/>
       <c r="H22" s="25"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="32"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="30"/>
       <c r="K22" s="25"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="32"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="30"/>
       <c r="Q22" s="25"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="32"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="30"/>
       <c r="T22" s="25"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="32"/>
-      <c r="W22" s="28"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="32"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="29"/>
+      <c r="Y22" s="30"/>
       <c r="Z22" s="25"/>
-      <c r="AA22" s="31"/>
-      <c r="AB22" s="32"/>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="30"/>
       <c r="AC22" s="25"/>
-      <c r="AD22" s="31"/>
-      <c r="AE22" s="32"/>
-      <c r="AF22" s="36"/>
-      <c r="AG22" s="31"/>
-      <c r="AH22" s="32"/>
-      <c r="AI22" s="28"/>
-      <c r="AJ22" s="31"/>
-      <c r="AK22" s="32"/>
+      <c r="AD22" s="29"/>
+      <c r="AE22" s="30"/>
+      <c r="AF22" s="33"/>
+      <c r="AG22" s="29"/>
+      <c r="AH22" s="30"/>
+      <c r="AI22" s="25"/>
+      <c r="AJ22" s="29"/>
+      <c r="AK22" s="30"/>
       <c r="AL22" s="25"/>
-      <c r="AM22" s="31"/>
-      <c r="AN22" s="32"/>
+      <c r="AM22" s="29"/>
+      <c r="AN22" s="30"/>
       <c r="AO22" s="25"/>
-      <c r="AP22" s="31"/>
-      <c r="AQ22" s="32"/>
+      <c r="AP22" s="29"/>
+      <c r="AQ22" s="30"/>
       <c r="AR22" s="25"/>
-      <c r="AS22" s="31"/>
-      <c r="AT22" s="32"/>
-      <c r="AU22" s="36"/>
-      <c r="AV22" s="31"/>
-      <c r="AW22" s="32"/>
+      <c r="AS22" s="29"/>
+      <c r="AT22" s="30"/>
+      <c r="AU22" s="33"/>
+      <c r="AV22" s="29"/>
+      <c r="AW22" s="30"/>
       <c r="AX22" s="25"/>
-      <c r="AY22" s="31"/>
-      <c r="AZ22" s="32"/>
-    </row>
-    <row r="23" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A23" s="39" t="s">
-        <v>92</v>
-      </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="32"/>
+      <c r="AY22" s="29"/>
+      <c r="AZ22" s="30"/>
+      <c r="BB22" s="45"/>
+      <c r="BC22" s="45"/>
+    </row>
+    <row r="23" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A23" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="25"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="30"/>
       <c r="H23" s="25"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="32"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="30"/>
       <c r="K23" s="25"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="32"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="30"/>
       <c r="Q23" s="25"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="32"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="30"/>
       <c r="T23" s="25"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="32"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="30"/>
       <c r="Z23" s="25"/>
-      <c r="AA23" s="31"/>
-      <c r="AB23" s="32"/>
+      <c r="AA23" s="29"/>
+      <c r="AB23" s="30"/>
       <c r="AC23" s="25"/>
-      <c r="AD23" s="31"/>
-      <c r="AE23" s="32"/>
-      <c r="AF23" s="28"/>
-      <c r="AG23" s="31"/>
-      <c r="AH23" s="32"/>
-      <c r="AI23" s="28"/>
-      <c r="AJ23" s="31"/>
-      <c r="AK23" s="32"/>
+      <c r="AD23" s="29"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="29"/>
+      <c r="AH23" s="30"/>
+      <c r="AI23" s="25"/>
+      <c r="AJ23" s="29"/>
+      <c r="AK23" s="30"/>
       <c r="AL23" s="25"/>
-      <c r="AM23" s="31"/>
-      <c r="AN23" s="32"/>
+      <c r="AM23" s="29"/>
+      <c r="AN23" s="30"/>
       <c r="AO23" s="25"/>
-      <c r="AP23" s="31"/>
-      <c r="AQ23" s="32"/>
+      <c r="AP23" s="29"/>
+      <c r="AQ23" s="30"/>
       <c r="AR23" s="25"/>
-      <c r="AS23" s="31"/>
-      <c r="AT23" s="32"/>
-      <c r="AU23" s="29"/>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="32"/>
-      <c r="AX23" s="29"/>
-      <c r="AY23" s="31"/>
-      <c r="AZ23" s="32"/>
-    </row>
-    <row r="24" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A24" s="37" t="s">
-        <v>93</v>
+      <c r="AS23" s="29"/>
+      <c r="AT23" s="30"/>
+      <c r="AU23" s="28"/>
+      <c r="AV23" s="47"/>
+      <c r="AW23" s="30"/>
+      <c r="AX23" s="28"/>
+      <c r="AY23" s="29"/>
+      <c r="AZ23" s="30"/>
+      <c r="BB23" s="45"/>
+      <c r="BC23" s="45"/>
+    </row>
+    <row r="24" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A24" s="34" t="s">
+        <v>97</v>
       </c>
       <c r="B24" s="25"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="32"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="30"/>
       <c r="H24" s="25"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="32"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="30"/>
       <c r="K24" s="25"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="31"/>
-      <c r="P24" s="32"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="30"/>
       <c r="Q24" s="25"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="32"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="30"/>
       <c r="T24" s="25"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="32"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="30"/>
       <c r="W24" s="25"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="28"/>
-      <c r="AA24" s="31"/>
-      <c r="AB24" s="32"/>
-      <c r="AC24" s="28"/>
-      <c r="AD24" s="31"/>
-      <c r="AE24" s="32"/>
-      <c r="AF24" s="28"/>
-      <c r="AG24" s="31"/>
-      <c r="AH24" s="32"/>
+      <c r="X24" s="29"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="29"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="29"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="29"/>
+      <c r="AH24" s="30"/>
       <c r="AI24" s="25"/>
-      <c r="AJ24" s="31"/>
-      <c r="AK24" s="32"/>
-      <c r="AL24" s="28"/>
-      <c r="AM24" s="31"/>
-      <c r="AN24" s="32"/>
+      <c r="AJ24" s="29"/>
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="25"/>
+      <c r="AM24" s="29"/>
+      <c r="AN24" s="30"/>
       <c r="AO24" s="25"/>
-      <c r="AP24" s="31"/>
-      <c r="AQ24" s="32"/>
+      <c r="AP24" s="29"/>
+      <c r="AQ24" s="30"/>
       <c r="AR24" s="25"/>
-      <c r="AS24" s="31"/>
-      <c r="AT24" s="32"/>
-      <c r="AU24" s="29"/>
-      <c r="AV24" s="49"/>
-      <c r="AW24" s="32"/>
-      <c r="AX24" s="29"/>
-      <c r="AY24" s="31"/>
-      <c r="AZ24" s="32"/>
-    </row>
-    <row r="25" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A25" s="37" t="s">
-        <v>94</v>
+      <c r="AS24" s="29"/>
+      <c r="AT24" s="30"/>
+      <c r="AU24" s="28"/>
+      <c r="AV24" s="47"/>
+      <c r="AW24" s="30"/>
+      <c r="AX24" s="28"/>
+      <c r="AY24" s="29"/>
+      <c r="AZ24" s="30"/>
+      <c r="BB24" s="45"/>
+      <c r="BC24" s="45"/>
+    </row>
+    <row r="25" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A25" s="34" t="s">
+        <v>98</v>
       </c>
       <c r="B25" s="25"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="32"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="25"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="32"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="32"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="30"/>
       <c r="T25" s="25"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="32"/>
-      <c r="W25" s="28"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="32"/>
-      <c r="Z25" s="28"/>
-      <c r="AA25" s="31"/>
-      <c r="AB25" s="32"/>
-      <c r="AC25" s="28"/>
-      <c r="AD25" s="31"/>
-      <c r="AE25" s="32"/>
-      <c r="AF25" s="28"/>
-      <c r="AG25" s="31"/>
-      <c r="AH25" s="32"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="29"/>
+      <c r="AB25" s="30"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="29"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="29"/>
+      <c r="AH25" s="30"/>
       <c r="AI25" s="25"/>
-      <c r="AJ25" s="31"/>
-      <c r="AK25" s="32"/>
+      <c r="AJ25" s="29"/>
+      <c r="AK25" s="30"/>
       <c r="AL25" s="25"/>
-      <c r="AM25" s="31"/>
-      <c r="AN25" s="32"/>
+      <c r="AM25" s="29"/>
+      <c r="AN25" s="30"/>
       <c r="AO25" s="25"/>
-      <c r="AP25" s="31"/>
-      <c r="AQ25" s="32"/>
-      <c r="AR25" s="28"/>
-      <c r="AS25" s="31"/>
-      <c r="AT25" s="32"/>
-      <c r="AU25" s="28"/>
-      <c r="AV25" s="31"/>
-      <c r="AW25" s="32"/>
+      <c r="AP25" s="29"/>
+      <c r="AQ25" s="30"/>
+      <c r="AR25" s="25"/>
+      <c r="AS25" s="29"/>
+      <c r="AT25" s="30"/>
+      <c r="AU25" s="25"/>
+      <c r="AV25" s="29"/>
+      <c r="AW25" s="30"/>
       <c r="AX25" s="25"/>
-      <c r="AY25" s="31"/>
-      <c r="AZ25" s="32"/>
-    </row>
-    <row r="26" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A26" s="37" t="s">
-        <v>95</v>
+      <c r="AY25" s="29"/>
+      <c r="AZ25" s="30"/>
+      <c r="BB25" s="45"/>
+      <c r="BC25" s="45"/>
+    </row>
+    <row r="26" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A26" s="34" t="s">
+        <v>99</v>
       </c>
       <c r="B26" s="25"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="32"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="30"/>
       <c r="T26" s="25"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="32"/>
-      <c r="W26" s="28"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="32"/>
-      <c r="Z26" s="28"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="32"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="25"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="25"/>
+      <c r="AA26" s="29"/>
+      <c r="AB26" s="30"/>
       <c r="AC26" s="25"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="32"/>
-      <c r="AF26" s="28"/>
-      <c r="AG26" s="31"/>
-      <c r="AH26" s="32"/>
+      <c r="AD26" s="29"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="29"/>
+      <c r="AH26" s="30"/>
       <c r="AI26" s="25"/>
-      <c r="AJ26" s="31"/>
-      <c r="AK26" s="32"/>
+      <c r="AJ26" s="29"/>
+      <c r="AK26" s="30"/>
       <c r="AL26" s="25"/>
-      <c r="AM26" s="31"/>
-      <c r="AN26" s="32"/>
+      <c r="AM26" s="29"/>
+      <c r="AN26" s="30"/>
       <c r="AO26" s="25"/>
-      <c r="AP26" s="31"/>
-      <c r="AQ26" s="32"/>
-      <c r="AR26" s="28"/>
-      <c r="AS26" s="31"/>
-      <c r="AT26" s="32"/>
-      <c r="AU26" s="28"/>
-      <c r="AV26" s="31"/>
-      <c r="AW26" s="32"/>
+      <c r="AP26" s="29"/>
+      <c r="AQ26" s="30"/>
+      <c r="AR26" s="25"/>
+      <c r="AS26" s="29"/>
+      <c r="AT26" s="30"/>
+      <c r="AU26" s="25"/>
+      <c r="AV26" s="29"/>
+      <c r="AW26" s="30"/>
       <c r="AX26" s="25"/>
-      <c r="AY26" s="31"/>
-      <c r="AZ26" s="32"/>
-    </row>
-    <row r="27" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A27" s="37" t="s">
-        <v>96</v>
+      <c r="AY26" s="29"/>
+      <c r="AZ26" s="30"/>
+      <c r="BB26" s="45"/>
+      <c r="BC26" s="45"/>
+    </row>
+    <row r="27" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A27" s="34" t="s">
+        <v>100</v>
       </c>
       <c r="B27" s="25"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="31"/>
-      <c r="P27" s="32"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="30"/>
       <c r="Q27" s="25"/>
-      <c r="R27" s="31"/>
-      <c r="S27" s="32"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="30"/>
       <c r="T27" s="25"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="32"/>
-      <c r="W27" s="28"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="32"/>
-      <c r="Z27" s="28"/>
-      <c r="AA27" s="31"/>
-      <c r="AB27" s="32"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="25"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="25"/>
+      <c r="AA27" s="29"/>
+      <c r="AB27" s="30"/>
       <c r="AC27" s="25"/>
-      <c r="AD27" s="31"/>
-      <c r="AE27" s="32"/>
-      <c r="AF27" s="28"/>
-      <c r="AG27" s="31"/>
-      <c r="AH27" s="32"/>
+      <c r="AD27" s="29"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="29"/>
+      <c r="AH27" s="30"/>
       <c r="AI27" s="25"/>
-      <c r="AJ27" s="31"/>
-      <c r="AK27" s="32"/>
+      <c r="AJ27" s="29"/>
+      <c r="AK27" s="30"/>
       <c r="AL27" s="25"/>
-      <c r="AM27" s="31"/>
-      <c r="AN27" s="32"/>
+      <c r="AM27" s="29"/>
+      <c r="AN27" s="30"/>
       <c r="AO27" s="25"/>
-      <c r="AP27" s="31"/>
-      <c r="AQ27" s="32"/>
-      <c r="AR27" s="28"/>
-      <c r="AS27" s="31"/>
-      <c r="AT27" s="32"/>
-      <c r="AU27" s="28"/>
-      <c r="AV27" s="31"/>
-      <c r="AW27" s="32"/>
+      <c r="AP27" s="29"/>
+      <c r="AQ27" s="30"/>
+      <c r="AR27" s="25"/>
+      <c r="AS27" s="29"/>
+      <c r="AT27" s="30"/>
+      <c r="AU27" s="25"/>
+      <c r="AV27" s="29"/>
+      <c r="AW27" s="30"/>
       <c r="AX27" s="25"/>
-      <c r="AY27" s="31"/>
-      <c r="AZ27" s="32"/>
-    </row>
-    <row r="28" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A28" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="32"/>
-      <c r="T28" s="28"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="32"/>
-      <c r="W28" s="28"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="32"/>
-      <c r="Z28" s="28"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="32"/>
-      <c r="AC28" s="28"/>
-      <c r="AD28" s="31"/>
-      <c r="AE28" s="32"/>
-      <c r="AF28" s="28"/>
-      <c r="AG28" s="31"/>
-      <c r="AH28" s="32"/>
+      <c r="AY27" s="29"/>
+      <c r="AZ27" s="30"/>
+      <c r="BB27" s="45"/>
+      <c r="BC27" s="45"/>
+    </row>
+    <row r="28" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A28" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="25"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="25"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="25"/>
+      <c r="AA28" s="29"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="29"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="25"/>
+      <c r="AG28" s="29"/>
+      <c r="AH28" s="30"/>
       <c r="AI28" s="25"/>
-      <c r="AJ28" s="31"/>
-      <c r="AK28" s="32"/>
-      <c r="AL28" s="28"/>
-      <c r="AM28" s="31"/>
-      <c r="AN28" s="32"/>
+      <c r="AJ28" s="29"/>
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="25"/>
+      <c r="AM28" s="29"/>
+      <c r="AN28" s="30"/>
       <c r="AO28" s="25"/>
-      <c r="AP28" s="31"/>
-      <c r="AQ28" s="32"/>
+      <c r="AP28" s="29"/>
+      <c r="AQ28" s="30"/>
       <c r="AR28" s="25"/>
-      <c r="AS28" s="31"/>
-      <c r="AT28" s="32"/>
-      <c r="AU28" s="28"/>
-      <c r="AV28" s="31"/>
-      <c r="AW28" s="32"/>
+      <c r="AS28" s="29"/>
+      <c r="AT28" s="30"/>
+      <c r="AU28" s="25"/>
+      <c r="AV28" s="29"/>
+      <c r="AW28" s="30"/>
       <c r="AX28" s="25"/>
-      <c r="AY28" s="31"/>
-      <c r="AZ28" s="32"/>
-    </row>
-    <row r="29" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A29" s="39" t="s">
-        <v>98</v>
+      <c r="AY28" s="29"/>
+      <c r="AZ28" s="30"/>
+      <c r="BB28" s="45"/>
+      <c r="BC28" s="45"/>
+    </row>
+    <row r="29" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A29" s="36" t="s">
+        <v>102</v>
       </c>
       <c r="B29" s="25"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="32"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="30"/>
       <c r="K29" s="25"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="50"/>
-      <c r="S29" s="32"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="30"/>
       <c r="T29" s="25"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="32"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="50"/>
-      <c r="Y29" s="32"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="50"/>
-      <c r="AB29" s="32"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="25"/>
+      <c r="AA29" s="48"/>
+      <c r="AB29" s="30"/>
       <c r="AC29" s="25"/>
-      <c r="AD29" s="31"/>
-      <c r="AE29" s="32"/>
+      <c r="AD29" s="29"/>
+      <c r="AE29" s="30"/>
       <c r="AF29" s="25"/>
-      <c r="AG29" s="31"/>
-      <c r="AH29" s="32"/>
+      <c r="AG29" s="29"/>
+      <c r="AH29" s="30"/>
       <c r="AI29" s="25"/>
-      <c r="AJ29" s="31"/>
-      <c r="AK29" s="32"/>
+      <c r="AJ29" s="29"/>
+      <c r="AK29" s="30"/>
       <c r="AL29" s="25"/>
-      <c r="AM29" s="31"/>
-      <c r="AN29" s="32"/>
+      <c r="AM29" s="29"/>
+      <c r="AN29" s="30"/>
       <c r="AO29" s="25"/>
-      <c r="AP29" s="31"/>
-      <c r="AQ29" s="32"/>
+      <c r="AP29" s="29"/>
+      <c r="AQ29" s="30"/>
       <c r="AR29" s="25"/>
-      <c r="AS29" s="31"/>
-      <c r="AT29" s="32"/>
-      <c r="AU29" s="36"/>
-      <c r="AV29" s="31"/>
-      <c r="AW29" s="32"/>
+      <c r="AS29" s="29"/>
+      <c r="AT29" s="30"/>
+      <c r="AU29" s="33"/>
+      <c r="AV29" s="29"/>
+      <c r="AW29" s="30"/>
       <c r="AX29" s="25"/>
-      <c r="AY29" s="31"/>
-      <c r="AZ29" s="32"/>
-    </row>
-    <row r="30" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A30" s="39" t="s">
-        <v>99</v>
+      <c r="AY29" s="29"/>
+      <c r="AZ29" s="30"/>
+      <c r="BB29" s="45"/>
+      <c r="BC29" s="45"/>
+    </row>
+    <row r="30" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A30" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="B30" s="25"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="32"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="30"/>
       <c r="K30" s="25"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="28"/>
-      <c r="O30" s="31"/>
-      <c r="P30" s="32"/>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="31"/>
-      <c r="S30" s="32"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="30"/>
       <c r="T30" s="25"/>
-      <c r="U30" s="31"/>
-      <c r="V30" s="32"/>
-      <c r="W30" s="29"/>
-      <c r="X30" s="31"/>
-      <c r="Y30" s="32"/>
-      <c r="Z30" s="28"/>
-      <c r="AA30" s="31"/>
-      <c r="AB30" s="32"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="28"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="25"/>
+      <c r="AA30" s="29"/>
+      <c r="AB30" s="30"/>
       <c r="AC30" s="25"/>
-      <c r="AD30" s="31"/>
-      <c r="AE30" s="32"/>
+      <c r="AD30" s="29"/>
+      <c r="AE30" s="30"/>
       <c r="AF30" s="25"/>
-      <c r="AG30" s="31"/>
-      <c r="AH30" s="32"/>
+      <c r="AG30" s="29"/>
+      <c r="AH30" s="30"/>
       <c r="AI30" s="25"/>
-      <c r="AJ30" s="31"/>
-      <c r="AK30" s="32"/>
+      <c r="AJ30" s="29"/>
+      <c r="AK30" s="30"/>
       <c r="AL30" s="25"/>
-      <c r="AM30" s="31"/>
-      <c r="AN30" s="32"/>
+      <c r="AM30" s="29"/>
+      <c r="AN30" s="30"/>
       <c r="AO30" s="25"/>
-      <c r="AP30" s="31"/>
-      <c r="AQ30" s="32"/>
+      <c r="AP30" s="29"/>
+      <c r="AQ30" s="30"/>
       <c r="AR30" s="25"/>
-      <c r="AS30" s="31"/>
-      <c r="AT30" s="32"/>
-      <c r="AU30" s="36"/>
-      <c r="AV30" s="31"/>
-      <c r="AW30" s="32"/>
+      <c r="AS30" s="29"/>
+      <c r="AT30" s="30"/>
+      <c r="AU30" s="33"/>
+      <c r="AV30" s="29"/>
+      <c r="AW30" s="30"/>
       <c r="AX30" s="25"/>
-      <c r="AY30" s="31"/>
-      <c r="AZ30" s="32"/>
-    </row>
-    <row r="31" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A31" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="32"/>
+      <c r="AY30" s="29"/>
+      <c r="AZ30" s="30"/>
+      <c r="BB30" s="45"/>
+      <c r="BC30" s="45"/>
+    </row>
+    <row r="31" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A31" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="25"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="25"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="32"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30"/>
       <c r="H31" s="25"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="32"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="30"/>
       <c r="K31" s="25"/>
-      <c r="L31" s="51"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="32"/>
+      <c r="L31" s="49"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="49"/>
+      <c r="P31" s="30"/>
       <c r="Q31" s="25"/>
-      <c r="R31" s="51"/>
-      <c r="S31" s="32"/>
+      <c r="R31" s="49"/>
+      <c r="S31" s="30"/>
       <c r="T31" s="25"/>
-      <c r="U31" s="51"/>
-      <c r="V31" s="32"/>
-      <c r="W31" s="29"/>
-      <c r="X31" s="31"/>
-      <c r="Y31" s="32"/>
+      <c r="U31" s="49"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="28"/>
+      <c r="X31" s="29"/>
+      <c r="Y31" s="30"/>
       <c r="Z31" s="25"/>
-      <c r="AA31" s="51"/>
-      <c r="AB31" s="32"/>
+      <c r="AA31" s="49"/>
+      <c r="AB31" s="30"/>
       <c r="AC31" s="25"/>
-      <c r="AD31" s="51"/>
-      <c r="AE31" s="32"/>
+      <c r="AD31" s="49"/>
+      <c r="AE31" s="30"/>
       <c r="AF31" s="25"/>
-      <c r="AG31" s="51"/>
-      <c r="AH31" s="32"/>
+      <c r="AG31" s="49"/>
+      <c r="AH31" s="30"/>
       <c r="AI31" s="25"/>
-      <c r="AJ31" s="51"/>
-      <c r="AK31" s="32"/>
+      <c r="AJ31" s="49"/>
+      <c r="AK31" s="30"/>
       <c r="AL31" s="25"/>
-      <c r="AM31" s="51"/>
-      <c r="AN31" s="32"/>
-      <c r="AO31" s="28"/>
-      <c r="AP31" s="51"/>
-      <c r="AQ31" s="32"/>
+      <c r="AM31" s="49"/>
+      <c r="AN31" s="30"/>
+      <c r="AO31" s="25"/>
+      <c r="AP31" s="49"/>
+      <c r="AQ31" s="30"/>
       <c r="AR31" s="25"/>
-      <c r="AS31" s="51"/>
-      <c r="AT31" s="32"/>
+      <c r="AS31" s="49"/>
+      <c r="AT31" s="30"/>
       <c r="AU31" s="25"/>
-      <c r="AV31" s="51"/>
-      <c r="AW31" s="32"/>
+      <c r="AV31" s="49"/>
+      <c r="AW31" s="30"/>
       <c r="AX31" s="25"/>
-      <c r="AY31" s="51"/>
-      <c r="AZ31" s="32"/>
-    </row>
-    <row r="32" ht="22.05" customHeight="1" spans="1:54">
-      <c r="A32" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="B32" s="52"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="32"/>
-      <c r="N32" s="52"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="32"/>
-      <c r="Q32" s="53"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="32"/>
-      <c r="T32" s="53"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="32"/>
-      <c r="W32" s="53"/>
-      <c r="X32" s="31"/>
-      <c r="Y32" s="32"/>
-      <c r="Z32" s="52"/>
-      <c r="AA32" s="31"/>
-      <c r="AB32" s="32"/>
-      <c r="AC32" s="53"/>
-      <c r="AD32" s="31"/>
-      <c r="AE32" s="32"/>
-      <c r="AF32" s="52"/>
-      <c r="AG32" s="31"/>
-      <c r="AH32" s="32"/>
-      <c r="AI32" s="53"/>
-      <c r="AJ32" s="31"/>
-      <c r="AK32" s="32"/>
-      <c r="AL32" s="52"/>
-      <c r="AM32" s="31"/>
-      <c r="AN32" s="32"/>
-      <c r="AO32" s="52"/>
-      <c r="AP32" s="31"/>
-      <c r="AQ32" s="32"/>
-      <c r="AR32" s="53"/>
-      <c r="AS32" s="31"/>
-      <c r="AT32" s="32"/>
-      <c r="AU32" s="52"/>
-      <c r="AV32" s="31"/>
-      <c r="AW32" s="32"/>
-      <c r="AX32" s="53"/>
-      <c r="AY32" s="31"/>
-      <c r="AZ32" s="32"/>
-    </row>
-    <row r="33" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A33" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="40"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="40"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="43"/>
-      <c r="O33" s="40"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="43"/>
-      <c r="R33" s="40"/>
-      <c r="S33" s="41"/>
-      <c r="T33" s="43"/>
-      <c r="U33" s="40"/>
-      <c r="V33" s="41"/>
-      <c r="W33" s="43"/>
-      <c r="X33" s="40"/>
-      <c r="Y33" s="41"/>
-      <c r="Z33" s="43"/>
-      <c r="AA33" s="40"/>
-      <c r="AB33" s="41"/>
-      <c r="AC33" s="43"/>
-      <c r="AD33" s="40"/>
-      <c r="AE33" s="41"/>
-      <c r="AF33" s="43"/>
-      <c r="AG33" s="40"/>
-      <c r="AH33" s="41"/>
-      <c r="AI33" s="43"/>
-      <c r="AJ33" s="40"/>
-      <c r="AK33" s="41"/>
-      <c r="AL33" s="43"/>
-      <c r="AM33" s="40"/>
-      <c r="AN33" s="41"/>
-      <c r="AO33" s="43"/>
-      <c r="AP33" s="40"/>
-      <c r="AQ33" s="41"/>
-      <c r="AR33" s="43"/>
-      <c r="AS33" s="40"/>
-      <c r="AT33" s="41"/>
-      <c r="AU33" s="43"/>
-      <c r="AV33" s="40"/>
-      <c r="AW33" s="41"/>
-      <c r="AX33" s="43"/>
-      <c r="AY33" s="40"/>
-      <c r="AZ33" s="41"/>
-    </row>
-    <row r="34" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A34" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="47"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="47"/>
-      <c r="I34" s="40"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="47"/>
-      <c r="L34" s="40"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="40"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="40"/>
-      <c r="S34" s="41"/>
-      <c r="T34" s="47"/>
-      <c r="U34" s="40"/>
-      <c r="V34" s="41"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="40"/>
-      <c r="Y34" s="41"/>
-      <c r="Z34" s="47"/>
-      <c r="AA34" s="40"/>
-      <c r="AB34" s="41"/>
-      <c r="AC34" s="47"/>
-      <c r="AD34" s="40"/>
-      <c r="AE34" s="41"/>
-      <c r="AF34" s="47"/>
-      <c r="AG34" s="40"/>
-      <c r="AH34" s="41"/>
-      <c r="AI34" s="47"/>
-      <c r="AJ34" s="40"/>
-      <c r="AK34" s="41"/>
-      <c r="AL34" s="47"/>
-      <c r="AM34" s="40"/>
-      <c r="AN34" s="41"/>
-      <c r="AO34" s="47"/>
-      <c r="AP34" s="40"/>
-      <c r="AQ34" s="41"/>
-      <c r="AR34" s="47"/>
-      <c r="AS34" s="40"/>
-      <c r="AT34" s="41"/>
-      <c r="AU34" s="47"/>
-      <c r="AV34" s="40"/>
-      <c r="AW34" s="41"/>
-      <c r="AX34" s="47"/>
-      <c r="AY34" s="40"/>
-      <c r="AZ34" s="41"/>
-    </row>
-    <row r="35" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A35" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="54"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="54"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="54"/>
-      <c r="I35" s="55"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="54"/>
-      <c r="L35" s="55"/>
-      <c r="M35" s="56"/>
-      <c r="N35" s="54"/>
-      <c r="O35" s="55"/>
-      <c r="P35" s="56"/>
-      <c r="Q35" s="54"/>
-      <c r="R35" s="55"/>
-      <c r="S35" s="56"/>
-      <c r="T35" s="57"/>
-      <c r="U35" s="58"/>
-      <c r="V35" s="59"/>
-      <c r="W35" s="57"/>
-      <c r="X35" s="58"/>
-      <c r="Y35" s="59"/>
-      <c r="Z35" s="57"/>
-      <c r="AA35" s="58"/>
-      <c r="AB35" s="59"/>
-      <c r="AC35" s="57"/>
-      <c r="AD35" s="58"/>
-      <c r="AE35" s="59"/>
-      <c r="AF35" s="57"/>
-      <c r="AG35" s="58"/>
-      <c r="AH35" s="59"/>
-      <c r="AI35" s="57"/>
-      <c r="AJ35" s="58"/>
-      <c r="AK35" s="59"/>
-      <c r="AL35" s="57"/>
-      <c r="AM35" s="58"/>
-      <c r="AN35" s="59"/>
-      <c r="AO35" s="57"/>
-      <c r="AP35" s="58"/>
-      <c r="AQ35" s="59"/>
-      <c r="AR35" s="57"/>
-      <c r="AS35" s="58"/>
-      <c r="AT35" s="59"/>
-      <c r="AU35" s="57"/>
-      <c r="AV35" s="58"/>
-      <c r="AW35" s="59"/>
-      <c r="AX35" s="57"/>
-      <c r="AY35" s="58"/>
-      <c r="AZ35" s="59"/>
-    </row>
-    <row r="36" spans="1:52">
+      <c r="AY31" s="49"/>
+      <c r="AZ31" s="30"/>
+      <c r="BB31" s="45"/>
+      <c r="BC31" s="45"/>
+    </row>
+    <row r="32" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A32" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" s="50"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="50"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="50"/>
+      <c r="X32" s="29"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="50"/>
+      <c r="AA32" s="29"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="50"/>
+      <c r="AD32" s="29"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="50"/>
+      <c r="AG32" s="29"/>
+      <c r="AH32" s="30"/>
+      <c r="AI32" s="50"/>
+      <c r="AJ32" s="29"/>
+      <c r="AK32" s="30"/>
+      <c r="AL32" s="50"/>
+      <c r="AM32" s="29"/>
+      <c r="AN32" s="30"/>
+      <c r="AO32" s="50"/>
+      <c r="AP32" s="29"/>
+      <c r="AQ32" s="30"/>
+      <c r="AR32" s="50"/>
+      <c r="AS32" s="29"/>
+      <c r="AT32" s="30"/>
+      <c r="AU32" s="50"/>
+      <c r="AV32" s="29"/>
+      <c r="AW32" s="30"/>
+      <c r="AX32" s="50"/>
+      <c r="AY32" s="29"/>
+      <c r="AZ32" s="30"/>
+      <c r="BB32" s="45"/>
+      <c r="BC32" s="45"/>
+    </row>
+    <row r="33" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A33" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="40"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="37"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="37"/>
+      <c r="P33" s="38"/>
+      <c r="Q33" s="40"/>
+      <c r="R33" s="37"/>
+      <c r="S33" s="38"/>
+      <c r="T33" s="40"/>
+      <c r="U33" s="37"/>
+      <c r="V33" s="38"/>
+      <c r="W33" s="40"/>
+      <c r="X33" s="37"/>
+      <c r="Y33" s="38"/>
+      <c r="Z33" s="40"/>
+      <c r="AA33" s="37"/>
+      <c r="AB33" s="38"/>
+      <c r="AC33" s="40"/>
+      <c r="AD33" s="37"/>
+      <c r="AE33" s="38"/>
+      <c r="AF33" s="40"/>
+      <c r="AG33" s="37"/>
+      <c r="AH33" s="38"/>
+      <c r="AI33" s="40"/>
+      <c r="AJ33" s="37"/>
+      <c r="AK33" s="38"/>
+      <c r="AL33" s="40"/>
+      <c r="AM33" s="37"/>
+      <c r="AN33" s="38"/>
+      <c r="AO33" s="40"/>
+      <c r="AP33" s="37"/>
+      <c r="AQ33" s="38"/>
+      <c r="AR33" s="40"/>
+      <c r="AS33" s="37"/>
+      <c r="AT33" s="38"/>
+      <c r="AU33" s="40"/>
+      <c r="AV33" s="37"/>
+      <c r="AW33" s="38"/>
+      <c r="AX33" s="40"/>
+      <c r="AY33" s="37"/>
+      <c r="AZ33" s="38"/>
+      <c r="BB33" s="45"/>
+      <c r="BC33" s="45"/>
+    </row>
+    <row r="34" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A34" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="44"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="44"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="44"/>
+      <c r="O34" s="37"/>
+      <c r="P34" s="38"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="37"/>
+      <c r="S34" s="38"/>
+      <c r="T34" s="44"/>
+      <c r="U34" s="37"/>
+      <c r="V34" s="38"/>
+      <c r="W34" s="44"/>
+      <c r="X34" s="37"/>
+      <c r="Y34" s="38"/>
+      <c r="Z34" s="44"/>
+      <c r="AA34" s="37"/>
+      <c r="AB34" s="38"/>
+      <c r="AC34" s="44"/>
+      <c r="AD34" s="37"/>
+      <c r="AE34" s="38"/>
+      <c r="AF34" s="44"/>
+      <c r="AG34" s="37"/>
+      <c r="AH34" s="38"/>
+      <c r="AI34" s="44"/>
+      <c r="AJ34" s="37"/>
+      <c r="AK34" s="38"/>
+      <c r="AL34" s="44"/>
+      <c r="AM34" s="37"/>
+      <c r="AN34" s="38"/>
+      <c r="AO34" s="44"/>
+      <c r="AP34" s="37"/>
+      <c r="AQ34" s="38"/>
+      <c r="AR34" s="44"/>
+      <c r="AS34" s="37"/>
+      <c r="AT34" s="38"/>
+      <c r="AU34" s="44"/>
+      <c r="AV34" s="37"/>
+      <c r="AW34" s="38"/>
+      <c r="AX34" s="44"/>
+      <c r="AY34" s="37"/>
+      <c r="AZ34" s="38"/>
+      <c r="BB34" s="45"/>
+      <c r="BC34" s="45"/>
+    </row>
+    <row r="35" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A35" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="51"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="51"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="51"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="53"/>
+      <c r="Q35" s="51"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="53"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="55"/>
+      <c r="V35" s="56"/>
+      <c r="W35" s="54"/>
+      <c r="X35" s="55"/>
+      <c r="Y35" s="56"/>
+      <c r="Z35" s="54"/>
+      <c r="AA35" s="55"/>
+      <c r="AB35" s="56"/>
+      <c r="AC35" s="54"/>
+      <c r="AD35" s="55"/>
+      <c r="AE35" s="56"/>
+      <c r="AF35" s="54"/>
+      <c r="AG35" s="55"/>
+      <c r="AH35" s="56"/>
+      <c r="AI35" s="54"/>
+      <c r="AJ35" s="55"/>
+      <c r="AK35" s="56"/>
+      <c r="AL35" s="54"/>
+      <c r="AM35" s="55"/>
+      <c r="AN35" s="56"/>
+      <c r="AO35" s="54"/>
+      <c r="AP35" s="55"/>
+      <c r="AQ35" s="56"/>
+      <c r="AR35" s="54"/>
+      <c r="AS35" s="55"/>
+      <c r="AT35" s="56"/>
+      <c r="AU35" s="54"/>
+      <c r="AV35" s="55"/>
+      <c r="AW35" s="56"/>
+      <c r="AX35" s="54"/>
+      <c r="AY35" s="55"/>
+      <c r="AZ35" s="56"/>
+      <c r="BB35" s="45"/>
+      <c r="BC35" s="45"/>
+    </row>
+    <row r="36" spans="1:55">
       <c r="A36" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" s="61"/>
-      <c r="D36" s="62"/>
-      <c r="E36" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="F36" s="61"/>
-      <c r="G36" s="62"/>
-      <c r="H36" s="60" t="s">
-        <v>107</v>
-      </c>
-      <c r="I36" s="61"/>
-      <c r="J36" s="62"/>
-      <c r="K36" s="60" t="s">
-        <v>108</v>
-      </c>
-      <c r="L36" s="61"/>
-      <c r="M36" s="62"/>
-      <c r="N36" s="60" t="s">
+      <c r="B36" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="O36" s="61"/>
-      <c r="P36" s="62"/>
-      <c r="Q36" s="60" t="s">
+      <c r="C36" s="58"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="57" t="s">
         <v>110</v>
       </c>
-      <c r="R36" s="61"/>
-      <c r="S36" s="62"/>
-    </row>
-    <row r="37" ht="14.25" customHeight="1" spans="1:52">
+      <c r="F36" s="58"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="I36" s="58"/>
+      <c r="J36" s="59"/>
+      <c r="K36" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="L36" s="58"/>
+      <c r="M36" s="59"/>
+      <c r="N36" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="O36" s="58"/>
+      <c r="P36" s="59"/>
+      <c r="Q36" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="R36" s="58"/>
+      <c r="S36" s="59"/>
+      <c r="BB36" s="45"/>
+      <c r="BC36" s="45"/>
+    </row>
+    <row r="37" ht="14.25" customHeight="1" spans="1:55">
       <c r="A37" s="16"/>
-      <c r="B37" s="63"/>
-      <c r="C37" s="64"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="64"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="65"/>
-      <c r="K37" s="63"/>
-      <c r="L37" s="64"/>
-      <c r="M37" s="65"/>
-      <c r="N37" s="63"/>
-      <c r="O37" s="64"/>
-      <c r="P37" s="65"/>
-      <c r="Q37" s="63"/>
-      <c r="R37" s="64"/>
-      <c r="S37" s="65"/>
-    </row>
-    <row r="38" ht="27.75" customHeight="1" spans="1:52">
-      <c r="A38" s="66" t="s">
+      <c r="B37" s="60"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="62"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="62"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="62"/>
+      <c r="K37" s="60"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="62"/>
+      <c r="N37" s="60"/>
+      <c r="O37" s="61"/>
+      <c r="P37" s="62"/>
+      <c r="Q37" s="60"/>
+      <c r="R37" s="61"/>
+      <c r="S37" s="62"/>
+      <c r="BB37" s="45"/>
+      <c r="BC37" s="45"/>
+    </row>
+    <row r="38" ht="27.75" customHeight="1" spans="1:55">
+      <c r="A38" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="B38" s="67" t="s">
+      <c r="B38" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="68" t="s">
+      <c r="C38" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="D38" s="69" t="s">
+      <c r="D38" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="E38" s="67" t="s">
+      <c r="E38" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="F38" s="68" t="s">
+      <c r="F38" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="69" t="s">
+      <c r="G38" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="H38" s="67" t="s">
+      <c r="H38" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="I38" s="68" t="s">
+      <c r="I38" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="J38" s="69" t="s">
+      <c r="J38" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="K38" s="67" t="s">
+      <c r="K38" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="L38" s="68" t="s">
+      <c r="L38" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="M38" s="69" t="s">
+      <c r="M38" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="N38" s="67" t="s">
+      <c r="N38" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="O38" s="68" t="s">
+      <c r="O38" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="P38" s="69" t="s">
+      <c r="P38" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="Q38" s="67" t="s">
+      <c r="Q38" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="R38" s="68" t="s">
+      <c r="R38" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="S38" s="69" t="s">
+      <c r="S38" s="66" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="39" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A39" s="70" t="s">
+      <c r="BB38" s="45"/>
+      <c r="BC38" s="45"/>
+    </row>
+    <row r="39" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A39" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="71"/>
+      <c r="B39" s="50"/>
       <c r="C39" s="26"/>
       <c r="D39" s="27"/>
-      <c r="E39" s="28"/>
+      <c r="E39" s="25"/>
       <c r="F39" s="26"/>
       <c r="G39" s="27"/>
-      <c r="H39" s="28"/>
+      <c r="H39" s="25"/>
       <c r="I39" s="26"/>
       <c r="J39" s="27"/>
       <c r="K39" s="25"/>
       <c r="L39" s="26"/>
       <c r="M39" s="27"/>
-      <c r="N39" s="28"/>
+      <c r="N39" s="25"/>
       <c r="O39" s="26"/>
       <c r="P39" s="27"/>
-      <c r="Q39" s="28"/>
+      <c r="Q39" s="25"/>
       <c r="R39" s="26"/>
       <c r="S39" s="27"/>
     </row>
-    <row r="40" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A40" s="72" t="s">
+    <row r="40" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A40" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="71"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="32"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="32"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="31"/>
-      <c r="S40" s="32"/>
-    </row>
-    <row r="41" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A41" s="72" t="s">
+      <c r="B40" s="50"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="25"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="25"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="30"/>
+    </row>
+    <row r="41" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A41" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B41" s="71"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="32"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="31"/>
-      <c r="P41" s="32"/>
-      <c r="Q41" s="28"/>
-      <c r="R41" s="31"/>
-      <c r="S41" s="32"/>
-    </row>
-    <row r="42" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A42" s="73" t="s">
+      <c r="B41" s="50"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="25"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="30"/>
+      <c r="Q41" s="25"/>
+      <c r="R41" s="29"/>
+      <c r="S41" s="30"/>
+    </row>
+    <row r="42" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A42" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="34"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="32"/>
-      <c r="N42" s="34"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="32"/>
-      <c r="Q42" s="34"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="32"/>
-    </row>
-    <row r="43" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A43" s="73" t="s">
+      <c r="B42" s="32"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="32"/>
+      <c r="R42" s="29"/>
+      <c r="S42" s="30"/>
+    </row>
+    <row r="43" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A43" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="34"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="34"/>
-      <c r="L43" s="31"/>
-      <c r="M43" s="32"/>
-      <c r="N43" s="34"/>
-      <c r="O43" s="31"/>
-      <c r="P43" s="32"/>
-      <c r="Q43" s="34"/>
-      <c r="R43" s="31"/>
-      <c r="S43" s="32"/>
-    </row>
-    <row r="44" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A44" s="74" t="s">
+      <c r="B43" s="32"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="32"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="30"/>
+    </row>
+    <row r="44" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A44" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="75"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="31"/>
-      <c r="M44" s="32"/>
-      <c r="N44" s="28"/>
-      <c r="O44" s="31"/>
-      <c r="P44" s="32"/>
-      <c r="Q44" s="28"/>
-      <c r="R44" s="31"/>
-      <c r="S44" s="32"/>
-    </row>
-    <row r="45" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A45" s="74" t="s">
+      <c r="B44" s="50"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="29"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="25"/>
+      <c r="O44" s="29"/>
+      <c r="P44" s="30"/>
+      <c r="Q44" s="25"/>
+      <c r="R44" s="29"/>
+      <c r="S44" s="30"/>
+    </row>
+    <row r="45" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A45" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="71"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="31"/>
-      <c r="M45" s="32"/>
-      <c r="N45" s="28"/>
-      <c r="O45" s="31"/>
-      <c r="P45" s="32"/>
-      <c r="Q45" s="28"/>
-      <c r="R45" s="31"/>
-      <c r="S45" s="32"/>
-    </row>
-    <row r="46" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A46" s="74" t="s">
+      <c r="B45" s="50"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="25"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="30"/>
+      <c r="N45" s="25"/>
+      <c r="O45" s="29"/>
+      <c r="P45" s="30"/>
+      <c r="Q45" s="25"/>
+      <c r="R45" s="29"/>
+      <c r="S45" s="30"/>
+    </row>
+    <row r="46" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A46" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="71"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="32"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="31"/>
-      <c r="M46" s="32"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="32"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="31"/>
-      <c r="S46" s="32"/>
-    </row>
-    <row r="47" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A47" s="74" t="s">
+      <c r="B46" s="50"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="25"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="25"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="25"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="30"/>
+    </row>
+    <row r="47" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A47" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="71"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="32"/>
+      <c r="B47" s="50"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="30"/>
       <c r="E47" s="25"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="31"/>
-      <c r="M47" s="32"/>
-      <c r="N47" s="28"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="32"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="25"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="25"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="30"/>
       <c r="Q47" s="25"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="32"/>
-    </row>
-    <row r="48" ht="22.05" customHeight="1" spans="1:52">
-      <c r="A48" s="74" t="s">
+      <c r="R47" s="29"/>
+      <c r="S47" s="30"/>
+    </row>
+    <row r="48" ht="22.05" customHeight="1" spans="1:55">
+      <c r="A48" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="71"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="32"/>
+      <c r="B48" s="50"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="30"/>
       <c r="E48" s="25"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="32"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="30"/>
       <c r="H48" s="25"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="31"/>
-      <c r="M48" s="32"/>
-      <c r="N48" s="28"/>
-      <c r="O48" s="31"/>
-      <c r="P48" s="32"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="25"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="25"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="30"/>
       <c r="Q48" s="25"/>
-      <c r="R48" s="31"/>
-      <c r="S48" s="32"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="30"/>
     </row>
     <row r="49" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A49" s="76" t="s">
+      <c r="A49" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="B49" s="77"/>
-      <c r="C49" s="40"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="40"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="43"/>
-      <c r="L49" s="40"/>
-      <c r="M49" s="41"/>
-      <c r="N49" s="43"/>
-      <c r="O49" s="40"/>
-      <c r="P49" s="41"/>
-      <c r="Q49" s="43"/>
-      <c r="R49" s="40"/>
-      <c r="S49" s="41"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="40"/>
+      <c r="I49" s="37"/>
+      <c r="J49" s="38"/>
+      <c r="K49" s="40"/>
+      <c r="L49" s="37"/>
+      <c r="M49" s="38"/>
+      <c r="N49" s="40"/>
+      <c r="O49" s="37"/>
+      <c r="P49" s="38"/>
+      <c r="Q49" s="40"/>
+      <c r="R49" s="37"/>
+      <c r="S49" s="38"/>
     </row>
     <row r="50" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A50" s="76" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50" s="77"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="43"/>
-      <c r="L50" s="40"/>
-      <c r="M50" s="41"/>
-      <c r="N50" s="43"/>
-      <c r="O50" s="40"/>
-      <c r="P50" s="41"/>
-      <c r="Q50" s="43"/>
-      <c r="R50" s="40"/>
-      <c r="S50" s="41"/>
+      <c r="A50" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B50" s="68"/>
+      <c r="C50" s="37"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="37"/>
+      <c r="J50" s="38"/>
+      <c r="K50" s="40"/>
+      <c r="L50" s="37"/>
+      <c r="M50" s="38"/>
+      <c r="N50" s="40"/>
+      <c r="O50" s="37"/>
+      <c r="P50" s="38"/>
+      <c r="Q50" s="40"/>
+      <c r="R50" s="37"/>
+      <c r="S50" s="38"/>
     </row>
     <row r="51" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A51" s="74" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="78" t="s">
+      <c r="A51" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="D51" s="41"/>
-      <c r="E51" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="F51" s="44"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="46" t="s">
+      <c r="C51" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="D51" s="38"/>
+      <c r="E51" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="F51" s="41"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="I51" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="J51" s="41"/>
-      <c r="K51" s="46" t="s">
+      <c r="I51" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="J51" s="38"/>
+      <c r="K51" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="L51" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="M51" s="41"/>
-      <c r="N51" s="46" t="s">
+      <c r="L51" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="M51" s="38"/>
+      <c r="N51" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="O51" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="R51" s="44"/>
-      <c r="S51" s="41"/>
+      <c r="O51" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="P51" s="38"/>
+      <c r="Q51" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="R51" s="41"/>
+      <c r="S51" s="38"/>
     </row>
     <row r="52" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A52" s="74" t="s">
-        <v>66</v>
-      </c>
-      <c r="B52" s="78" t="s">
+      <c r="A52" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="B52" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="D52" s="41"/>
-      <c r="E52" s="46" t="s">
+      <c r="C52" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" s="38"/>
+      <c r="E52" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F52" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="G52" s="41"/>
-      <c r="H52" s="46" t="s">
+      <c r="F52" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="G52" s="38"/>
+      <c r="H52" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="I52" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="J52" s="41"/>
-      <c r="K52" s="46" t="s">
+      <c r="I52" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="J52" s="38"/>
+      <c r="K52" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="L52" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="M52" s="41"/>
-      <c r="N52" s="46" t="s">
+      <c r="L52" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="M52" s="38"/>
+      <c r="N52" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="O52" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="P52" s="41"/>
-      <c r="Q52" s="46" t="s">
+      <c r="O52" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="P52" s="38"/>
+      <c r="Q52" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="R52" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="S52" s="41"/>
+      <c r="R52" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="S52" s="38"/>
     </row>
     <row r="53" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A53" s="74" t="s">
-        <v>73</v>
-      </c>
-      <c r="B53" s="79" t="s">
+      <c r="A53" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="C53" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="D53" s="41"/>
-      <c r="E53" s="42" t="s">
+      <c r="C53" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" s="38"/>
+      <c r="E53" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="F53" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="G53" s="41"/>
-      <c r="H53" s="42" t="s">
+      <c r="F53" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="G53" s="38"/>
+      <c r="H53" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="I53" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="J53" s="41"/>
-      <c r="K53" s="42" t="s">
+      <c r="I53" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="J53" s="38"/>
+      <c r="K53" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="L53" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="M53" s="41"/>
-      <c r="N53" s="42" t="s">
+      <c r="L53" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="M53" s="38"/>
+      <c r="N53" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="O53" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="P53" s="41"/>
-      <c r="Q53" s="42" t="s">
+      <c r="O53" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="P53" s="38"/>
+      <c r="Q53" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="R53" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="S53" s="41"/>
+      <c r="R53" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="S53" s="38"/>
     </row>
     <row r="54" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A54" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="78" t="s">
+      <c r="A54" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="D54" s="41"/>
-      <c r="E54" s="46" t="s">
+      <c r="C54" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" s="38"/>
+      <c r="E54" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F54" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="G54" s="41"/>
-      <c r="H54" s="46" t="s">
+      <c r="F54" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="G54" s="38"/>
+      <c r="H54" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="I54" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="J54" s="41"/>
-      <c r="K54" s="46" t="s">
+      <c r="I54" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="J54" s="38"/>
+      <c r="K54" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="L54" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="M54" s="41"/>
-      <c r="N54" s="46" t="s">
+      <c r="L54" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="M54" s="38"/>
+      <c r="N54" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="O54" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="P54" s="41"/>
-      <c r="Q54" s="46" t="s">
+      <c r="O54" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="P54" s="38"/>
+      <c r="Q54" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="R54" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="S54" s="41"/>
+      <c r="R54" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="S54" s="38"/>
     </row>
     <row r="55" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A55" s="74" t="s">
-        <v>87</v>
-      </c>
-      <c r="B55" s="78" t="s">
+      <c r="A55" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="B55" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" s="41"/>
-      <c r="E55" s="46" t="s">
+      <c r="C55" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D55" s="38"/>
+      <c r="E55" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="F55" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="G55" s="41"/>
-      <c r="H55" s="46" t="s">
+      <c r="F55" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="G55" s="38"/>
+      <c r="H55" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="I55" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="J55" s="41"/>
-      <c r="K55" s="46" t="s">
+      <c r="I55" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="J55" s="38"/>
+      <c r="K55" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="L55" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="M55" s="41"/>
-      <c r="N55" s="46" t="s">
+      <c r="L55" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="M55" s="38"/>
+      <c r="N55" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="O55" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="P55" s="41"/>
-      <c r="Q55" s="46" t="s">
+      <c r="O55" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="P55" s="38"/>
+      <c r="Q55" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="R55" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="S55" s="41"/>
+      <c r="R55" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="S55" s="38"/>
     </row>
     <row r="56" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A56" s="76" t="s">
-        <v>91</v>
-      </c>
-      <c r="B56" s="80"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="47"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="47"/>
-      <c r="I56" s="40"/>
-      <c r="J56" s="41"/>
-      <c r="K56" s="47"/>
-      <c r="L56" s="40"/>
-      <c r="M56" s="41"/>
-      <c r="N56" s="47"/>
-      <c r="O56" s="40"/>
-      <c r="P56" s="41"/>
-      <c r="Q56" s="47"/>
-      <c r="R56" s="40"/>
-      <c r="S56" s="41"/>
+      <c r="A56" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B56" s="71"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="37"/>
+      <c r="J56" s="38"/>
+      <c r="K56" s="44"/>
+      <c r="L56" s="37"/>
+      <c r="M56" s="38"/>
+      <c r="N56" s="44"/>
+      <c r="O56" s="37"/>
+      <c r="P56" s="38"/>
+      <c r="Q56" s="44"/>
+      <c r="R56" s="37"/>
+      <c r="S56" s="38"/>
     </row>
     <row r="57" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A57" s="76" t="s">
-        <v>92</v>
-      </c>
-      <c r="B57" s="80"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="47"/>
-      <c r="I57" s="40"/>
-      <c r="J57" s="41"/>
-      <c r="K57" s="47"/>
-      <c r="L57" s="40"/>
-      <c r="M57" s="41"/>
-      <c r="N57" s="47"/>
-      <c r="O57" s="40"/>
-      <c r="P57" s="41"/>
-      <c r="Q57" s="47"/>
-      <c r="R57" s="40"/>
-      <c r="S57" s="41"/>
+      <c r="A57" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" s="71"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="37"/>
+      <c r="J57" s="38"/>
+      <c r="K57" s="44"/>
+      <c r="L57" s="37"/>
+      <c r="M57" s="38"/>
+      <c r="N57" s="44"/>
+      <c r="O57" s="37"/>
+      <c r="P57" s="38"/>
+      <c r="Q57" s="44"/>
+      <c r="R57" s="37"/>
+      <c r="S57" s="38"/>
     </row>
     <row r="58" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A58" s="74" t="s">
-        <v>93</v>
-      </c>
-      <c r="B58" s="71"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="31"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="32"/>
-      <c r="N58" s="28"/>
-      <c r="O58" s="31"/>
-      <c r="P58" s="32"/>
-      <c r="Q58" s="28"/>
-      <c r="R58" s="31"/>
-      <c r="S58" s="32"/>
+      <c r="A58" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B58" s="50"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="25"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="25"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="25"/>
+      <c r="R58" s="29"/>
+      <c r="S58" s="30"/>
     </row>
     <row r="59" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A59" s="74" t="s">
-        <v>94</v>
-      </c>
-      <c r="B59" s="71"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="28"/>
-      <c r="L59" s="31"/>
-      <c r="M59" s="32"/>
-      <c r="N59" s="28"/>
-      <c r="O59" s="31"/>
-      <c r="P59" s="32"/>
-      <c r="Q59" s="28"/>
-      <c r="R59" s="31"/>
-      <c r="S59" s="32"/>
+      <c r="A59" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B59" s="50"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="29"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="25"/>
+      <c r="L59" s="29"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="25"/>
+      <c r="O59" s="29"/>
+      <c r="P59" s="30"/>
+      <c r="Q59" s="25"/>
+      <c r="R59" s="29"/>
+      <c r="S59" s="30"/>
     </row>
     <row r="60" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A60" s="74" t="s">
-        <v>95</v>
-      </c>
-      <c r="B60" s="71"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="31"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="31"/>
-      <c r="J60" s="32"/>
-      <c r="K60" s="28"/>
-      <c r="L60" s="31"/>
-      <c r="M60" s="32"/>
-      <c r="N60" s="28"/>
-      <c r="O60" s="31"/>
-      <c r="P60" s="32"/>
-      <c r="Q60" s="28"/>
-      <c r="R60" s="31"/>
-      <c r="S60" s="32"/>
+      <c r="A60" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60" s="50"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="29"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="25"/>
+      <c r="L60" s="29"/>
+      <c r="M60" s="30"/>
+      <c r="N60" s="25"/>
+      <c r="O60" s="29"/>
+      <c r="P60" s="30"/>
+      <c r="Q60" s="25"/>
+      <c r="R60" s="29"/>
+      <c r="S60" s="30"/>
     </row>
     <row r="61" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A61" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="32"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="32"/>
-      <c r="N61" s="28"/>
-      <c r="O61" s="31"/>
-      <c r="P61" s="32"/>
-      <c r="Q61" s="28"/>
-      <c r="R61" s="31"/>
-      <c r="S61" s="32"/>
+      <c r="A61" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="B61" s="50"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="25"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="25"/>
+      <c r="O61" s="29"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="25"/>
+      <c r="R61" s="29"/>
+      <c r="S61" s="30"/>
     </row>
     <row r="62" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A62" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="B62" s="71"/>
-      <c r="C62" s="31"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="28"/>
-      <c r="F62" s="31"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="31"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="28"/>
-      <c r="L62" s="31"/>
-      <c r="M62" s="32"/>
-      <c r="N62" s="28"/>
-      <c r="O62" s="31"/>
-      <c r="P62" s="32"/>
-      <c r="Q62" s="28"/>
-      <c r="R62" s="31"/>
-      <c r="S62" s="32"/>
+      <c r="A62" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B62" s="50"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="29"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="29"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="25"/>
+      <c r="L62" s="29"/>
+      <c r="M62" s="30"/>
+      <c r="N62" s="25"/>
+      <c r="O62" s="29"/>
+      <c r="P62" s="30"/>
+      <c r="Q62" s="25"/>
+      <c r="R62" s="29"/>
+      <c r="S62" s="30"/>
     </row>
     <row r="63" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A63" s="76" t="s">
-        <v>98</v>
-      </c>
-      <c r="B63" s="75"/>
-      <c r="C63" s="51"/>
-      <c r="D63" s="32"/>
+      <c r="A63" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B63" s="50"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="30"/>
       <c r="E63" s="25"/>
-      <c r="F63" s="51"/>
-      <c r="G63" s="32"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="30"/>
       <c r="H63" s="25"/>
-      <c r="I63" s="51"/>
-      <c r="J63" s="32"/>
+      <c r="I63" s="49"/>
+      <c r="J63" s="30"/>
       <c r="K63" s="25"/>
-      <c r="L63" s="51"/>
-      <c r="M63" s="32"/>
+      <c r="L63" s="49"/>
+      <c r="M63" s="30"/>
       <c r="N63" s="25"/>
-      <c r="O63" s="51"/>
-      <c r="P63" s="32"/>
+      <c r="O63" s="49"/>
+      <c r="P63" s="30"/>
       <c r="Q63" s="25"/>
-      <c r="R63" s="51"/>
-      <c r="S63" s="32"/>
+      <c r="R63" s="49"/>
+      <c r="S63" s="30"/>
     </row>
     <row r="64" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A64" s="76" t="s">
-        <v>99</v>
-      </c>
-      <c r="B64" s="75"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="32"/>
+      <c r="A64" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" s="50"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="30"/>
       <c r="E64" s="25"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="32"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="30"/>
       <c r="H64" s="25"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="32"/>
+      <c r="I64" s="29"/>
+      <c r="J64" s="30"/>
       <c r="K64" s="25"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="32"/>
+      <c r="L64" s="29"/>
+      <c r="M64" s="30"/>
       <c r="N64" s="25"/>
-      <c r="O64" s="31"/>
-      <c r="P64" s="32"/>
+      <c r="O64" s="29"/>
+      <c r="P64" s="30"/>
       <c r="Q64" s="25"/>
-      <c r="R64" s="31"/>
-      <c r="S64" s="32"/>
+      <c r="R64" s="29"/>
+      <c r="S64" s="30"/>
     </row>
     <row r="65" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A65" s="74" t="s">
-        <v>100</v>
-      </c>
-      <c r="B65" s="75"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="32"/>
+      <c r="A65" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B65" s="50"/>
+      <c r="C65" s="49"/>
+      <c r="D65" s="30"/>
       <c r="E65" s="25"/>
-      <c r="F65" s="51"/>
-      <c r="G65" s="32"/>
+      <c r="F65" s="49"/>
+      <c r="G65" s="30"/>
       <c r="H65" s="25"/>
-      <c r="I65" s="51"/>
-      <c r="J65" s="32"/>
+      <c r="I65" s="49"/>
+      <c r="J65" s="30"/>
       <c r="K65" s="25"/>
-      <c r="L65" s="51"/>
-      <c r="M65" s="32"/>
+      <c r="L65" s="49"/>
+      <c r="M65" s="30"/>
       <c r="N65" s="25"/>
-      <c r="O65" s="51"/>
-      <c r="P65" s="32"/>
+      <c r="O65" s="49"/>
+      <c r="P65" s="30"/>
       <c r="Q65" s="25"/>
-      <c r="R65" s="51"/>
-      <c r="S65" s="32"/>
+      <c r="R65" s="49"/>
+      <c r="S65" s="30"/>
     </row>
     <row r="66" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A66" s="74" t="s">
-        <v>101</v>
-      </c>
-      <c r="B66" s="52"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="52"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="52"/>
-      <c r="I66" s="31"/>
-      <c r="J66" s="32"/>
-      <c r="K66" s="52"/>
-      <c r="L66" s="31"/>
-      <c r="M66" s="32"/>
-      <c r="N66" s="52"/>
-      <c r="O66" s="31"/>
-      <c r="P66" s="32"/>
-      <c r="Q66" s="52"/>
-      <c r="R66" s="31"/>
-      <c r="S66" s="32"/>
+      <c r="A66" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="B66" s="50"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="50"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="50"/>
+      <c r="I66" s="29"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="50"/>
+      <c r="L66" s="29"/>
+      <c r="M66" s="30"/>
+      <c r="N66" s="50"/>
+      <c r="O66" s="29"/>
+      <c r="P66" s="30"/>
+      <c r="Q66" s="50"/>
+      <c r="R66" s="29"/>
+      <c r="S66" s="30"/>
     </row>
     <row r="67" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A67" s="74" t="s">
-        <v>102</v>
-      </c>
-      <c r="B67" s="77"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="41"/>
-      <c r="E67" s="43"/>
-      <c r="F67" s="40"/>
-      <c r="G67" s="41"/>
-      <c r="H67" s="43"/>
-      <c r="I67" s="40"/>
-      <c r="J67" s="41"/>
-      <c r="K67" s="43"/>
-      <c r="L67" s="40"/>
-      <c r="M67" s="41"/>
-      <c r="N67" s="43"/>
-      <c r="O67" s="40"/>
-      <c r="P67" s="41"/>
-      <c r="Q67" s="43"/>
-      <c r="R67" s="40"/>
-      <c r="S67" s="41"/>
+      <c r="A67" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="B67" s="68"/>
+      <c r="C67" s="37"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="38"/>
+      <c r="H67" s="40"/>
+      <c r="I67" s="37"/>
+      <c r="J67" s="38"/>
+      <c r="K67" s="40"/>
+      <c r="L67" s="37"/>
+      <c r="M67" s="38"/>
+      <c r="N67" s="40"/>
+      <c r="O67" s="37"/>
+      <c r="P67" s="38"/>
+      <c r="Q67" s="40"/>
+      <c r="R67" s="37"/>
+      <c r="S67" s="38"/>
     </row>
     <row r="68" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A68" s="74" t="s">
-        <v>103</v>
-      </c>
-      <c r="B68" s="80"/>
-      <c r="C68" s="40"/>
-      <c r="D68" s="41"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="40"/>
-      <c r="G68" s="41"/>
-      <c r="H68" s="47"/>
-      <c r="I68" s="40"/>
-      <c r="J68" s="41"/>
-      <c r="K68" s="47"/>
-      <c r="L68" s="40"/>
-      <c r="M68" s="41"/>
-      <c r="N68" s="47"/>
-      <c r="O68" s="40"/>
-      <c r="P68" s="41"/>
-      <c r="Q68" s="47"/>
-      <c r="R68" s="40"/>
-      <c r="S68" s="41"/>
+      <c r="A68" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="B68" s="71"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="44"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="38"/>
+      <c r="H68" s="44"/>
+      <c r="I68" s="37"/>
+      <c r="J68" s="38"/>
+      <c r="K68" s="44"/>
+      <c r="L68" s="37"/>
+      <c r="M68" s="38"/>
+      <c r="N68" s="44"/>
+      <c r="O68" s="37"/>
+      <c r="P68" s="38"/>
+      <c r="Q68" s="44"/>
+      <c r="R68" s="37"/>
+      <c r="S68" s="38"/>
     </row>
     <row r="69" ht="22.05" customHeight="1" spans="1:19">
-      <c r="A69" s="81" t="s">
-        <v>104</v>
-      </c>
-      <c r="B69" s="82"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="59"/>
-      <c r="E69" s="57"/>
-      <c r="F69" s="58"/>
-      <c r="G69" s="59"/>
-      <c r="H69" s="57"/>
-      <c r="I69" s="58"/>
-      <c r="J69" s="59"/>
-      <c r="K69" s="57"/>
-      <c r="L69" s="58"/>
-      <c r="M69" s="59"/>
-      <c r="N69" s="57"/>
-      <c r="O69" s="58"/>
-      <c r="P69" s="59"/>
-      <c r="Q69" s="57"/>
-      <c r="R69" s="58"/>
-      <c r="S69" s="59"/>
+      <c r="A69" s="72" t="s">
+        <v>108</v>
+      </c>
+      <c r="B69" s="73"/>
+      <c r="C69" s="55"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="54"/>
+      <c r="F69" s="55"/>
+      <c r="G69" s="56"/>
+      <c r="H69" s="54"/>
+      <c r="I69" s="55"/>
+      <c r="J69" s="56"/>
+      <c r="K69" s="54"/>
+      <c r="L69" s="55"/>
+      <c r="M69" s="56"/>
+      <c r="N69" s="54"/>
+      <c r="O69" s="55"/>
+      <c r="P69" s="56"/>
+      <c r="Q69" s="54"/>
+      <c r="R69" s="55"/>
+      <c r="S69" s="56"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B4:AZ41" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="26">
+  <mergeCells count="28">
     <mergeCell ref="H1:AZ1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A36:A37"/>
+    <mergeCell ref="BB18:BB38"/>
+    <mergeCell ref="BC18:BC38"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="E2:G3"/>
     <mergeCell ref="H2:J3"/>
